--- a/figures/parallel_verses/sidrac-melibeus.xlsx
+++ b/figures/parallel_verses/sidrac-melibeus.xlsx
@@ -512,7 +512,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.01734441464684233</v>
+        <v>0.01679927189901309</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>0.1575703603009697</v>
+        <v>0.1538768572331092</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.2245154862775091</v>
+        <v>0.2190203213746051</v>
       </c>
     </row>
     <row r="5">
@@ -632,7 +632,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.3665142712214534</v>
+        <v>0.3578951983347551</v>
       </c>
     </row>
     <row r="6">
@@ -672,7 +672,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.3852459505402147</v>
+        <v>0.3769189222060658</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.4195814122960545</v>
+        <v>0.4181910888895349</v>
       </c>
     </row>
     <row r="8">
@@ -752,7 +752,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.4342155464048677</v>
+        <v>0.43726077822826</v>
       </c>
     </row>
     <row r="9">
@@ -792,31 +792,31 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.4362632636788796</v>
+        <v>0.4380832550268456</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>158</v>
+        <v>27</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Die my int herte niet en ginc / Hebbic al gelaten uut</t>
+          <t>Aldus eest ende anders niet / Die de dinc te rechte besiet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>En hebbic niet in mi / Al woudic al laten varen</t>
+          <t>Es gheorloeft ende anders niet / Onder die droeve diet wel besiet</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>die ik in het hart niet ne gaan / hebben ik al laten uiten</t>
+          <t>aldus zijn het en anders niet / die de ding te rechte bezien</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ne hebben ik niet in ik / al willen ik al laten varen</t>
+          <t>zijn geoorloven en anders niet / onder die droef die het wel bezien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -832,31 +832,31 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.4674217759587678</v>
+        <v>0.4682399120039304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al in die stat tAntwerpen / Wast dat ic dit translateerde</t>
+          <t>Die anders doen sy doen quaet / Hoets hem elc dats mijn raet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ghetracteert uten latine / Al tAntwerpen in die poert</t>
+          <t>Want sonder voersieneghen raet / Doetmen dicke dat es quaet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>al in die stad te antwerpen / wassen dat ik dit translateren</t>
+          <t>die anders doen zij doen kwaad / hoe zij hij elk dat zijn mijn raad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>trakteren uit dat NOU-P / al te antwerpen in die port</t>
+          <t>want zonder voorzienigen raad / doen men dik dat zijn kwaad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -872,31 +872,31 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.4762755867560934</v>
+        <v>0.4733074473619566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aldus eest ende anders niet / Die de dinc te rechte besiet</t>
+          <t>Die my int herte niet en ginc / Hebbic al gelaten uut</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Es gheorloeft ende anders niet / Onder die droeve diet wel besiet</t>
+          <t>En hebbic niet in mi / Al woudic al laten varen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>aldus zijn het en anders niet / die de ding te rechte bezien</t>
+          <t>die ik in het hart niet ne gaan / hebben ik al laten uiten</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>zijn geoorloven en anders niet / onder die droef die het wel bezien</t>
+          <t>ne hebben ik niet in ik / al willen ik al laten varen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -912,31 +912,31 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.4779498999237478</v>
+        <v>0.476701515575174</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Die anders doen sy doen quaet / Hoets hem elc dats mijn raet</t>
+          <t>Al in die stat tAntwerpen / Wast dat ic dit translateerde</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Want sonder voersieneghen raet / Doetmen dicke dat es quaet</t>
+          <t>Ghetracteert uten latine / Al tAntwerpen in die poert</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>die anders doen zij doen kwaad / hoe zij hij elk dat zijn mijn raad</t>
+          <t>al in die stad te antwerpen / wassen dat ik dit translateren</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>want zonder voorzienigen raad / doen men dik dat zijn kwaad</t>
+          <t>trakteren uit dat NOU-P / al te antwerpen in die port</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -952,31 +952,31 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.484095127313661</v>
+        <v>0.4784341319853718</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daer ic in bescreven vant / Vele duechden ende wijsheden</t>
+          <t>Danne enighe erdsche rijchede / Want dese bouc hevet in</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Die wijsheyt heeft in den sin / Heeft alle doghet daer in</t>
+          <t>Sonder ertsche rijcheyt / Ende al dit ertsche beleyt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>daar ik in beschrijven vinden / veel deugd en wijsheid</t>
+          <t>dan enig aards rijkheid / want deze boek hebben in</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>die wijsheid hebben in de zin / hebben al deugd daar in</t>
+          <t>zonder aards rijkheid / en al dit aards beleid</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -992,31 +992,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.4912894529346128</v>
+        <v>0.4919710442789815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Danne enighe erdsche rijchede / Want dese bouc hevet in</t>
+          <t>Daer ic in bescreven vant / Vele duechden ende wijsheden</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sonder ertsche rijcheyt / Ende al dit ertsche beleyt</t>
+          <t>Men vint voer waer bescreven / Daer vele liede sijn dat daer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dan enig aards rijkheid / want deze boek hebben in</t>
+          <t>daar ik in beschrijven vinden / veel deugd en wijsheid</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>zonder aards rijkheid / en al dit aards beleid</t>
+          <t>men vinden voor waar beschrijven / daar veel lieden zijn dat daar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1032,31 +1032,31 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.4925034456293959</v>
+        <v>0.492963627545709</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Beide ter zielen ende ten live / Die ic hier na bescrive</t>
+          <t>Eenen onghelovighen coninc / Hiet Boctus die hem leerde dese dinc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Beyde an ziele ende aen live / Want al dat ic hier scrive</t>
+          <t>Salomon leert ons die coninc / Dat vrient gaet boven alle dinc</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>beide ter ziel en ten lijf / die ik hier na beschrijven</t>
+          <t>een ongelovig koning / heten NOU-P die hij leren deze ding</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>beide aan ziel en aan lijf / want al dat ik hier schrijven</t>
+          <t>NOU-P leren ons die koning / dat vriend gaan boven al ding</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1072,31 +1072,31 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>0.5084126721780249</v>
+        <v>0.5032123960389865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eenen onghelovighen coninc / Hiet Boctus die hem leerde dese dinc</t>
+          <t>Die een God sijn metten Vader / Dus heeft sy algader</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salomon leert ons die coninc / Dat vrient gaet boven alle dinc</t>
+          <t>Vanden ewighen Vader / Dat es volmaect algader</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>een ongelovig koning / heten NOU-P die hij leren deze ding</t>
+          <t>die een god zijn met de vader / dus hebben zij algader</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NOU-P leren ons die koning / dat vriend gaan boven al ding</t>
+          <t>van de eeuwig vader / dat zijn volmaakt algader</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1112,31 +1112,31 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>0.5132147156250659</v>
+        <v>0.5042003341438324</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>An leren mach vroech ende spade / In weet wat sire inne menen</t>
+          <t>Ende oec zal hi doen verstaen / Hoet metten achtersten zal gaen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dat ons hadde moghen vallen / Vrouwe nu willen wi vroech ende spade</t>
+          <t>Hoeden soude ende niet voert gaen / Ende doet mi oec mede verstaen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>aan leren mogen vroeg en spade / u weten wat zijn ik ne menen</t>
+          <t>en ook zullen hij doen verstaan / hoe het met de achterste zullen gaan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dat ons hebben mogen vallen / vrouwe nu willen wij vroeg en spade</t>
+          <t>hoeden zullen en niet voeren gaan / en doen ik ook mede verstaan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1152,31 +1152,31 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.5138681791214997</v>
+        <v>0.504811406788743</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ende oec zal hi doen verstaen / Hoet metten achtersten zal gaen</t>
+          <t>Beide ter zielen ende ten live / Die ic hier na bescrive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hoeden soude ende niet voert gaen / Ende doet mi oec mede verstaen</t>
+          <t>Beyde an ziele ende aen live / Want al dat ic hier scrive</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>en ook zullen hij doen verstaan / hoe het met de achterste zullen gaan</t>
+          <t>beide ter ziel en ten lijf / die ik hier na beschrijven</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hoeden zullen en niet voeren gaan / en doen ik ook mede verstaan</t>
+          <t>beide aan ziel en aan lijf / want al dat ik hier schrijven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,31 +1192,31 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.5146407974594651</v>
+        <v>0.5095395193626464</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Daer by eest openbare / Dat haer niet en es ontseit</t>
+          <t>An leren mach vroech ende spade / In weet wat sire inne menen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ende seyden openbaer / Dat haere raet niet goet en waer</t>
+          <t>Dat ons hadde moghen vallen / Vrouwe nu willen wi vroech ende spade</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>daar bij zijn het openbaar / dat zij niet ne zijn ontzeggen</t>
+          <t>aan leren mogen vroeg en spade / u weten wat zijn ik ne menen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>en zeggen openbaar / dat haar raad niet goed ne zijn</t>
+          <t>dat ons hebben mogen vallen / vrouwe nu willen wij vroeg en spade</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1232,31 +1232,31 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0.516264009656711</v>
+        <v>0.5107969298363338</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Die een God sijn metten Vader / Dus heeft sy algader</t>
+          <t>Daer by eest openbare / Dat haer niet en es ontseit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vanden ewighen Vader / Dat es volmaect algader</t>
+          <t>Ende seyden openbaer / Dat haere raet niet goet en waer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>die een god zijn met de vader / dus hebben zij algader</t>
+          <t>daar bij zijn het openbaar / dat zij niet ne zijn ontzeggen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>van de eeuwig vader / dat zijn volmaakt algader</t>
+          <t>en zeggen openbaar / dat haar raad niet goed ne zijn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1272,31 +1272,31 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>0.5163213954125169</v>
+        <v>0.5119949617335039</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daer na weder verhalen en can / Want die tijt es ons ghegeuen</t>
+          <t>Dat ic dit werc bringhe toe / Ende mijn leven betren zoe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tgoet machmen verhalen nochtan / Maer den tijt en verhaelt nieman</t>
+          <t>Ic salt u wel bringhen toe / Melibeus sprac doe</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>daar na weder verhalen ne kunnen / want die tijd zijn ons geven</t>
+          <t>dat ik dit werk brengen toezenden / en mijn leven beteren zo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>het goed mogen men verhalen nochtan / maar de tijd ne verhalen niemand</t>
+          <t>ik zullen het u wel brengen toezenden / NOU-P spreken toen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1312,31 +1312,31 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.5200955249657677</v>
+        <v>0.5127231260397718</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dat ic dit werc bringhe toe / Ende mijn leven betren zoe</t>
+          <t>Dat hi ons geve sine vrede / Ende sine helige minne mede</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ic salt u wel bringhen toe / Melibeus sprac doe</t>
+          <t>Waect ende heeft ghenen vrede / Ende waer dat vrede niet en es</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dat ik dit werk brengen toezenden / en mijn leven beteren zo</t>
+          <t>dat hij ons geven zijn vrede / en zijn heilig minne mede</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ik zullen het u wel brengen toezenden / NOU-P spreken toen</t>
+          <t>waken en hebben gene vrede / en waar dat vrede niet ne zijn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1352,31 +1352,31 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>0.5207589886658879</v>
+        <v>0.5163400133397331</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dat hi ons geve sine vrede / Ende sine helige minne mede</t>
+          <t>Ende vanden stenen die virtuit / Ende oec eenderhande sotterie</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Waect ende heeft ghenen vrede / Ende waer dat vrede niet en es</t>
+          <t>Maer ghi sult sueken twaren / Den sin ende sine vertuut</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dat hij ons geven zijn vrede / en zijn heilig minne mede</t>
+          <t>en van de steen die virtuut / en ook enerhande zotterij</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>waken en hebben gene vrede / en waar dat vrede niet ne zijn</t>
+          <t>maar gij zullen zoeken dat waar / de zin en zijn virtuut</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1392,31 +1392,31 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>0.525595261498651</v>
+        <v>0.5181690876541896</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Want vele beter es wijshede / Danne enighe erdsche rijchede</t>
+          <t>Omme dat ic van dier edelre leren / Een woert niet woude anders keren</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sonder ertsche rijcheyt / Ende al dit ertsche beleyt</t>
+          <t>Eest dan dat ghi u leren / Ter clergyen wert wilt keren</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>want veel goed zijn wijsheid / dan enig aards rijkheid</t>
+          <t>om dat ik van die edel leer / een woord niet willen anders keren</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>zonder aards rijkheid / en al dit aards beleid</t>
+          <t>zijn het dan dat gij u leer / ter clergie waart willen keren</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1432,31 +1432,31 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.5259160507721035</v>
+        <v>0.5218829939875701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ende vanden stenen die virtuit / Ende oec eenderhande sotterie</t>
+          <t>Want vele beter es wijshede / Danne enighe erdsche rijchede</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maer ghi sult sueken twaren / Den sin ende sine vertuut</t>
+          <t>Sonder ertsche rijcheyt / Ende al dit ertsche beleyt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>en van de steen die virtuut / en ook enerhande zotterij</t>
+          <t>want veel goed zijn wijsheid / dan enig aards rijkheid</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>maar gij zullen zoeken dat waar / de zin en zijn virtuut</t>
+          <t>zonder aards rijkheid / en al dit aards beleid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1472,31 +1472,31 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0.5282288698600692</v>
+        <v>0.5274920964786144</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Omme dat ic van dier edelre leren / Een woert niet woude anders keren</t>
+          <t>Die den tijt onledich maken / Met onoerboerliken saken</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eest dan dat ghi u leren / Ter clergyen wert wilt keren</t>
+          <t>Want si can voer alle saken / Den mensche wel met Gode maken</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>om dat ik van die edel leer / een woord niet willen anders keren</t>
+          <t>die de tijd onledig maken / met onoorbaarlijk zaak</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>zijn het dan dat gij u leer / ter clergie waart willen keren</t>
+          <t>want zij kunnen voor al zaak / de mens wel met NOU-P maken</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1512,31 +1512,31 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>0.5339184984625642</v>
+        <v>0.5281009389445914</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Die hem ane die boeke houden / Daer sy clene profijt inne leren</t>
+          <t>Daer na weder verhalen en can / Want die tijt es ons ghegeuen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Int boeke daer hi leert minnen / Een cleyne ader ende niet groet</t>
+          <t>Tgoet machmen verhalen nochtan / Maer den tijt en verhaelt nieman</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>die hij aan die beuk houden / daar zij klein profijt in leren</t>
+          <t>daar na weder verhalen ne kunnen / want die tijd zijn ons geven</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>in het beuk daar hij leren minnen / een klein ader en niet groot</t>
+          <t>het goed mogen men verhalen nochtan / maar de tijd ne verhalen niemand</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1552,31 +1552,31 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>0.537018243438715</v>
+        <v>0.5288878196409292</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verre van mi wille werpen / Al in die stat tAntwerpen</t>
+          <t>Ende te levene zo langhe stonde / Dat ic dit werc bringhe toe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sonder mi en moghedi doen niet / Al t Andwerpen daer ic wone</t>
+          <t>Ic salt u wel bringhen toe / Melibeus sprac doe</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ver van ik willen werpen / al in die stad te antwerpen</t>
+          <t>en te leven zo lang stonde / dat ik dit werk brengen toezenden</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>zonder ik ne mogen gij doen niet / al het antwerpen daar ik wonen</t>
+          <t>ik zullen het u wel brengen toezenden / NOU-P spreken toen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1592,31 +1592,31 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>0.5397371713238932</v>
+        <v>0.5340991907441091</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ende te levene zo langhe stonde / Dat ic dit werc bringhe toe</t>
+          <t>Die hem ane die boeke houden / Daer sy clene profijt inne leren</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ic salt u wel bringhen toe / Melibeus sprac doe</t>
+          <t>Int boeke daer hi leert minnen / Een cleyne ader ende niet groet</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>en te leven zo lang stonde / dat ik dit werk brengen toezenden</t>
+          <t>die hij aan die beuk houden / daar zij klein profijt in leren</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ik zullen het u wel brengen toezenden / NOU-P spreken toen</t>
+          <t>in het beuk daar hij leren minnen / een klein ader en niet groot</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1632,31 +1632,31 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>0.5397829319663283</v>
+        <v>0.541645490115916</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>208</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Die den tijt onledich maken / Met onoerboerliken saken</t>
+          <t>Verre van mi wille werpen / Al in die stat tAntwerpen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Want si can voer alle saken / Den mensche wel met Gode maken</t>
+          <t>Sonder mi en moghedi doen niet / Al t Andwerpen daer ic wone</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>die de tijd onledig maken / met onoorbaarlijk zaak</t>
+          <t>ver van ik willen werpen / al in die stad te antwerpen</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>want zij kunnen voor al zaak / de mens wel met NOU-P maken</t>
+          <t>zonder ik ne mogen gij doen niet / al het antwerpen daar ik wonen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1672,7 +1672,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>0.5400817949365369</v>
+        <v>0.5422407544076555</v>
       </c>
     </row>
     <row r="32">
@@ -1712,31 +1712,31 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>0.5439951951832278</v>
+        <v>0.5424455837892379</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dat hy sinen heylegen Geest sinde / In hore omme die dinc</t>
+          <t>Was philosophe ende astronomijn / Die God alsoe hadde vercoren</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dat maect in hem een leven / Dan wercter die heylighe Gheest inne</t>
+          <t>Hoe hemel ende erde sijn ghedaen / Wijsheyt vanghet astronomien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dat hij zijn heilig geest einden / in haar om die ding</t>
+          <t>zijn filosoof en astronomijn / die NOU-P alzo hebben verkiezen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>dat maken in hij een leven / dan werkt die heilig geest in</t>
+          <t>hoe hemel en aarde zijn doen / wijsheid vangen astronomijn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1752,7 +1752,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>0.548721975444266</v>
+        <v>0.5435694355800934</v>
       </c>
     </row>
     <row r="34">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ende hebben sulke boeke / Daer hi wijsheyt in besoeke</t>
+          <t>Ende doedi doghet of enech goet / Dat sal hi decken onder voet</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>en hebben zulk beuk / daar hij wijsheid in bezoeken</t>
+          <t>en doen gij deugd of enig goed / dat zullen hij dekken onder voet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1792,31 +1792,31 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0.5518228063809394</v>
+        <v>0.5442477798245511</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Was philosophe ende astronomijn / Die God alsoe hadde vercoren</t>
+          <t>Dat in de werelt soude gevallen / Ende hoe sy inden soude met allen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hoe hemel ende erde sijn ghedaen / Wijsheyt vanghet astronomien</t>
+          <t>Hoe die dinc was ghevallen / Ende bat vriendelike hen allen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>zijn filosoof en astronomijn / die NOU-P alzo hebben verkiezen</t>
+          <t>dat in de wereld zullen vallen / en hoe zij innen zullen met al</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>hoe hemel en aarde zijn doen / wijsheid vangen astronomijn</t>
+          <t>hoe die ding zijn vallen / en batten vriendelijk zij al</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1832,7 +1832,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.5522520045607286</v>
+        <v>0.5448113043804143</v>
       </c>
     </row>
     <row r="36">
@@ -1872,7 +1872,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.5539295752294284</v>
+        <v>0.5461681186560725</v>
       </c>
     </row>
     <row r="37">
@@ -1912,31 +1912,31 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0.5547623665885903</v>
+        <v>0.5465558308853473</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Want die leringe die es goet / Beide ter zielen ende ten live</t>
+          <t>Want rime alsoe wijt vinden / Doet dicke die materie winden</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Beyde an ziele ende aen live / Want al dat ic hier scrive</t>
+          <t>Hi sprac Die scalke rade vinden / Dat si op hem selven winden</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>want die lering die zijn goed / beide ter ziel en ten lijf</t>
+          <t>want rijm alzo wij het vinden / doen dik die materie winden</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>beide aan ziel en aan lijf / want al dat ik hier schrijven</t>
+          <t>hij spreken die schalk raad vinden / dat zij op hij zelf winden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1952,31 +1952,31 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>0.5553432088298966</v>
+        <v>0.5520949856258976</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dat in de werelt soude gevallen / Ende hoe sy inden soude met allen</t>
+          <t>Dat ic dit boec woude maken / Uten Walsche in Dietsche spraken</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hoe die dinc was ghevallen / Ende bat vriendelike hen allen</t>
+          <t>Salomon seghet Soete spraken / Connen vele vriende maken</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dat in de wereld zullen vallen / en hoe zij innen zullen met al</t>
+          <t>dat ik dit boek willen maken / uit dat Waals in Diets spraak</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>hoe die ding zijn vallen / en batten vriendelijk zij al</t>
+          <t>NOU-P zeggen zoet spraak / kunnen veel vriend maken</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1992,31 +1992,31 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>0.555838931567495</v>
+        <v>0.5524654948778213</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maria vol van genaden / Ende staet my in staden</t>
+          <t>Want die leringe die es goet / Beide ter zielen ende ten live</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Om dat si hem in daden / Ende in rade soude staen in staden</t>
+          <t>Beyde an ziele ende aen live / Want al dat ic hier scrive</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NOU-P vol van genade / en staan ik in stade</t>
+          <t>want die lering die zijn goed / beide ter ziel en ten lijf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>om dat zij hij in daad / en in raad zullen staan in stade</t>
+          <t>beide aan ziel en aan lijf / want al dat ik hier schrijven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2032,31 +2032,31 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>0.5580108163501761</v>
+        <v>0.5532773342118822</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Die nemmermeer no wijf no man / Daer na weder verhalen en can</t>
+          <t>Die de Vader alsoe minde / Dat hy sinen heylegen Geest sinde</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Die nemen en can noch gheven / Noch noyt en hadde leven</t>
+          <t>Die hi dien Chorienten sinde / Elc late hem ghenoeghen des</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>die nimmermeer noch wijf noch man / daar na weder verhalen ne kunnen</t>
+          <t>die de vader alzo minnen / dat hij zijn heilig geest einden</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>die nemen ne kunnen noch geven / noch nooit ne hebben leven</t>
+          <t>die hij dat choriënt einden / elk laten hij genoegen de</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2072,16 +2072,16 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>0.5606491103799189</v>
+        <v>0.5540085368418953</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Die de Vader alsoe minde / Dat hy sinen heylegen Geest sinde</t>
+          <t>Dat hy sinen heylegen Geest sinde / In hore omme die dinc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>die de vader alzo minnen / dat hij zijn heilig geest einden</t>
+          <t>dat hij zijn heilig geest einden / in haar om die ding</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2112,31 +2112,31 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>0.5621830351596535</v>
+        <v>0.5540347234183585</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>13</v>
+        <v>161</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Daer anders niet inne en leit / Dan der werelt ydelheit</t>
+          <t>Maria vol van genaden / Ende staet my in staden</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ende so verstijft in u rijcheyt / Dat al u dinc es ijdelheyt</t>
+          <t>Om dat si hem in daden / Ende in rade soude staen in staden</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>daar anders niet in ne liggen / dan de wereld ijdelheid</t>
+          <t>NOU-P vol van genade / en staan ik in stade</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>en zo verstijven in u rijkheid / dat al u ding zijn ijdelheid</t>
+          <t>om dat zij hij in daad / en in raad zullen staan in stade</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2152,31 +2152,31 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>0.5630741862596838</v>
+        <v>0.5562503403380118</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>131</v>
+        <v>13</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dit was naer Noe VIIIc iaer / Ende XLVII daer naer</t>
+          <t>Daer anders niet inne en leit / Dan der werelt ydelheit</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prudentia sprac daer naer / Die warenesse daer men met</t>
+          <t>Ende so verstijft in u rijcheyt / Dat al u dinc es ijdelheyt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dit zijn naar NOU-P achttiende jaar / en zevenenveertig daar naar</t>
+          <t>daar anders niet in ne liggen / dan de wereld ijdelheid</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NOU-P spreken daar naar / die waarnis daar men met</t>
+          <t>en zo verstijven in u rijkheid / dat al u ding zijn ijdelheid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2192,31 +2192,31 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>0.564514871206736</v>
+        <v>0.5564797032817426</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Want rime alsoe wijt vinden / Doet dicke die materie winden</t>
+          <t>Daer men wijsheit doget ende goet / Ende troest van allen goeden rade</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hi sprac Die scalke rade vinden / Dat si op hem selven winden</t>
+          <t>Dat dien raet niet en waer goet / Want des volx menechfuldechede</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>want rijm alzo wij het vinden / doen dik die materie winden</t>
+          <t>daar men wijsheid doen en goed / en troosten van al goed raad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>hij spreken die schalk raad vinden / dat zij op hij zelf winden</t>
+          <t>dat dat raad niet ne zijn goed / want de volk menigvoudigheid</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2232,31 +2232,31 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>0.5650563643046823</v>
+        <v>0.5565889656134402</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dat ic dit boec woude maken / Uten Walsche in Dietsche spraken</t>
+          <t>Dit was naer Noe VIIIc iaer / Ende XLVII daer naer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salomon seghet Soete spraken / Connen vele vriende maken</t>
+          <t>Prudentia sprac daer naer / Die warenesse daer men met</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>dat ik dit boek willen maken / uit dat Waals in Diets spraak</t>
+          <t>dit zijn naar NOU-P achttiende jaar / en zevenenveertig daar naar</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NOU-P zeggen zoet spraak / kunnen veel vriend maken</t>
+          <t>NOU-P spreken daar naar / die waarnis daar men met</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2272,31 +2272,31 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>0.5656330218167909</v>
+        <v>0.5583522994081355</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Met onoerboerliken saken / My dunct dat sy zere riesen</t>
+          <t>Ende oec some ander dinc / Die my int herte niet en ginc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nu hebdi uwen raet bedreven / Met jonghen sotten riesen</t>
+          <t>Die vinsteren in waren dinghen / Daer dese viande in ghinghen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>met onoorbaarlijk zaak / ik dunken dat zij zeer riezen</t>
+          <t>en ook som ander ding / die ik in het hart niet ne gaan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>nu hebben gij uw raad bedrijven / met jong zot riezen</t>
+          <t>die vinsteren in waar ding / daar deze vijand in gaan</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2312,31 +2312,31 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>0.5672852038243672</v>
+        <v>0.5612073343115893</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Daer men wijsheit doget ende goet / Ende troest van allen goeden rade</t>
+          <t>Met onoerboerliken saken / My dunct dat sy zere riesen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dat dien raet niet en waer goet / Want des volx menechfuldechede</t>
+          <t>Nu hebdi uwen raet bedreven / Met jonghen sotten riesen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>daar men wijsheid doen en goed / en troosten van al goed raad</t>
+          <t>met onoorbaarlijk zaak / ik dunken dat zij zeer riezen</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>dat dat raad niet ne zijn goed / want de volk menigvoudigheid</t>
+          <t>nu hebben gij uw raad bedrijven / met jong zot riezen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2352,31 +2352,31 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>0.5687077996299331</v>
+        <v>0.5612745300883576</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dan omme gemene zalichede / Al der goonre dieze lezen</t>
+          <t>Noch geen Walsch en verstaen / Want ic hope sonder waen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sonder sake voer waer gheseyt / Maer al om uwe salicheyt</t>
+          <t>Tullius doet ons verstaen / In allen orboren sonder waen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>dan om gemeen zaligheid / al de gonder die zij lezen</t>
+          <t>noch geen Waals ne verstaan / want ik hopen zonder waan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>zonder sake voor waar zeggen / maar al om uw zaligheid</t>
+          <t>NOU-P doen ons verstaan / in al oorbaar zonder waan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2392,31 +2392,31 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>0.568861438037384</v>
+        <v>0.5616435125339057</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Daer hi sinen omoet in togede / Dat hi ons geve sine vrede</t>
+          <t>Die drievuldicheit in hare / Daer by eest openbare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Daer bi willic uwen oetmoet / Aenscouwen oetmoet es so goet</t>
+          <t>Ende seyden openbaer / Dat haere raet niet goet en waer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>daar hij zijn ootmoed in togen / dat hij ons geven zijn vrede</t>
+          <t>die drievuldigheid in haar / daar bij zijn het openbaar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>daar bij willen ik uw ootmoed / aanschouwen ootmoed zijn zo goed</t>
+          <t>en zeggen openbaar / dat haar raad niet goed ne zijn</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2432,31 +2432,31 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>0.5715091489746088</v>
+        <v>0.562207666911162</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Na enen clerc wijs ende fijn / Was philosophe ende astronomijn</t>
+          <t>Dan omme gemene zalichede / Al der goonre dieze lezen</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philosophen ende medicinen / Andere clercken ende Surginen</t>
+          <t>Sonder sake voer waer gheseyt / Maer al om uwe salicheyt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>na een klerk wijs en fijn / zijn filosoof en astronomijn</t>
+          <t>dan om gemeen zaligheid / al de gonder die zij lezen</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>filosoof en medicijn / ander klerk en surgijn</t>
+          <t>zonder sake voor waar zeggen / maar al om uw zaligheid</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2472,31 +2472,31 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>0.5720582759372286</v>
+        <v>0.5622314919181471</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ende oec some ander dinc / Die my int herte niet en ginc</t>
+          <t>In hore omme die dinc / Dat sire den Sone by ontfinc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Die vinsteren in waren dinghen / Daer dese viande in ghinghen</t>
+          <t>Daer hi ane in ware dinc / Menschelike nature ontfinc</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>en ook som ander ding / die ik in het hart niet ne gaan</t>
+          <t>in haar om die ding / dat zijn de zoon bij ontvangen</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>die vinsteren in waar ding / daar deze vijand in gaan</t>
+          <t>daar hij aan in waar ding / menselijk natuur ontvangen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2512,31 +2512,31 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>0.5731705851735382</v>
+        <v>0.5623067147202645</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ende hoe die mensce soude leven / Dit boec was in Walsche bescreven</t>
+          <t>Hoets hem elc dats mijn raet / Dat ic dit werc ierst ane ginc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bescrijft oec Seneca / Die boven al dat leeft</t>
+          <t>Dat wi ane Gode hoe dat gaet / Emmer selen soeken raet</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>en hoe die mens zullen leven / dit boek zijn in Waals beschrijven</t>
+          <t>hoe zij hij elk dat zijn mijn raad / dat ik dit werk eerst eindigen gaan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>beschrijven ook NOU-P / die boven al dat leven</t>
+          <t>dat wij aan NOU-P hoe dat gaan / immer zullen zoeken raad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2552,31 +2552,31 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>0.5737336889697615</v>
+        <v>0.5629567148092761</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Noch geen Walsch en verstaen / Want ic hope sonder waen</t>
+          <t>Ende hoe die mensce soude leven / Dit boec was in Walsche bescreven</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tullius doet ons verstaen / In allen orboren sonder waen</t>
+          <t>Bescrijft oec Seneca / Die boven al dat leeft</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>noch geen Waals ne verstaan / want ik hopen zonder waan</t>
+          <t>en hoe die mens zullen leven / dit boek zijn in Waals beschrijven</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NOU-P doen ons verstaan / in al oorbaar zonder waan</t>
+          <t>beschrijven ook NOU-P / die boven al dat leven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2592,31 +2592,31 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>0.5738419798981658</v>
+        <v>0.5643004635667717</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Die drievuldicheit in hare / Daer by eest openbare</t>
+          <t>Die nemmermeer no wijf no man / Daer na weder verhalen en can</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ende seyden openbaer / Dat haere raet niet goet en waer</t>
+          <t>Die nemen en can noch gheven / Noch noyt en hadde leven</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>die drievuldigheid in haar / daar bij zijn het openbaar</t>
+          <t>die nimmermeer noch wijf noch man / daar na weder verhalen ne kunnen</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>en zeggen openbaar / dat haar raad niet goed ne zijn</t>
+          <t>die nemen ne kunnen noch geven / noch nooit ne hebben leven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2632,31 +2632,31 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>0.5739868547201707</v>
+        <v>0.5647524799347285</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hoets hem elc dats mijn raet / Dat ic dit werc ierst ane ginc</t>
+          <t>Doe hine metter gracie van Gode / Hadde bekeert te sinen ghebode</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dat wi ane Gode hoe dat gaet / Emmer selen soeken raet</t>
+          <t>Ghelijc sinen scepper sinen God / Daer hi af hadde sijn ghebot</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>hoe zij hij elk dat zijn mijn raad / dat ik dit werk eerst eindigen gaan</t>
+          <t>toen hij hij met de gratie van NOU-P / hebben bekeren te zijn gebod</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>dat wij aan NOU-P hoe dat gaan / immer zullen zoeken raad</t>
+          <t>gelijk zijn schepper zijn NOU-P / daar hij af hebben zijn gebod</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2672,31 +2672,31 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>0.574115174844409</v>
+        <v>0.5678486838500647</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Uten Grixe dat hy conste wale / Ende oec ute Ebreusche tale</t>
+          <t>Alst comt te minen laetsten stonden / Dat hi mi dan al mine zonden</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uten loye decretale / Ende uten lereren also wale</t>
+          <t>Maer droefheit om die sonden / Es penitentie tallen stonden</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>uit dat griks dat hij kunnen wel / en ook uit Ebreus taal</t>
+          <t>als het komen te mijn laat stond / dat hij ik dan al mijn zonde</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>uit dat looi decretaal / en uit dat leraar alzo wel</t>
+          <t>maar droefheid om die zonde / zijn penitentie te al stond</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2712,31 +2712,31 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>0.5744696773075235</v>
+        <v>0.5691740042229387</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>In hore omme die dinc / Dat sire den Sone by ontfinc</t>
+          <t>Na enen clerc wijs ende fijn / Was philosophe ende astronomijn</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Daer hi ane in ware dinc / Menschelike nature ontfinc</t>
+          <t>Hoe hemel ende erde sijn ghedaen / Wijsheyt vanghet astronomien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>in haar om die ding / dat zijn de zoon bij ontvangen</t>
+          <t>na een klerk wijs en fijn / zijn filosoof en astronomijn</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>daar hij aan in waar ding / menselijk natuur ontvangen</t>
+          <t>hoe hemel en aarde zijn doen / wijsheid vangen astronomijn</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2752,31 +2752,31 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>0.5751345081816248</v>
+        <v>0.5715111922517788</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Doe hine metter gracie van Gode / Hadde bekeert te sinen ghebode</t>
+          <t>Uten Grixe dat hy conste wale / Ende oec ute Ebreusche tale</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ghelijc sinen scepper sinen God / Daer hi af hadde sijn ghebot</t>
+          <t>Uten loye decretale / Ende uten lereren also wale</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>toen hij hij met de gratie van NOU-P / hebben bekeren te zijn gebod</t>
+          <t>uit dat griks dat hij kunnen wel / en ook uit Ebreus taal</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>gelijk zijn schepper zijn NOU-P / daar hij af hebben zijn gebod</t>
+          <t>uit dat looi decretaal / en uit dat leraar alzo wel</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2792,31 +2792,31 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>0.5794510731646008</v>
+        <v>0.5727887960611753</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>206</v>
+        <v>8</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alst comt te minen laetsten stonden / Dat hi mi dan al mine zonden</t>
+          <t>Daer men luttel orboers in vint / Nochtan half logene es ende mere</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Maer droefheit om die sonden / Es penitentie tallen stonden</t>
+          <t>Dat hi mesdoet maer nochtan / Eest meer scanden alse men vint</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>als het komen te mijn laat stond / dat hij ik dan al mijn zonde</t>
+          <t>daar men luttel oorbaar in vinden / nochtan half leugen zijn en meer</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>maar droefheid om die zonde / zijn penitentie te al stond</t>
+          <t>dat hij misdoen maar nochtan / zijn het meer schande als men vinden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2832,31 +2832,31 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>0.5816241055748395</v>
+        <v>0.5741457686305682</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Een woert niet woude anders keren / Dant die edele wise clerc</t>
+          <t>Hy es Vader gebenedijt / Des Soens daer ghi moeder af sijt</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dus selen clercken sijn die leren / Die hem ter wijsheyt willen keren</t>
+          <t>Na sinen wille gheschie mi / Sijn name si ghebenedijt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>een woord niet willen anders keren / dan het die edel wijs klerk</t>
+          <t>hij zijn vader benedijen / de zoens daar gij moeder af zijn</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>dus zullen klerk zijn die leren / die hij ter wijsheid willen keren</t>
+          <t>na zijn wil geschieden ik / zijn naam zij benedijen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2872,31 +2872,31 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>0.5820283475315278</v>
+        <v>0.5749057252813032</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>8</v>
+        <v>217</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Daer men luttel orboers in vint / Nochtan half logene es ende mere</t>
+          <t>Daer hi sinen omoet in togede / Dat hi ons geve sine vrede</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dat hi mesdoet maer nochtan / Eest meer scanden alse men vint</t>
+          <t>Daer bi willic uwen oetmoet / Aenscouwen oetmoet es so goet</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>daar men luttel oorbaar in vinden / nochtan half leugen zijn en meer</t>
+          <t>daar hij zijn ootmoed in togen / dat hij ons geven zijn vrede</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>dat hij misdoen maar nochtan / zijn het meer schande als men vinden</t>
+          <t>daar bij willen ik uw ootmoed / aanschouwen ootmoed zijn zo goed</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2912,31 +2912,31 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>0.582469414401056</v>
+        <v>0.5753932723798412</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Daer sonder ic nemmeer en ben / In dichte niet dat weet wale</t>
+          <t>Een woert niet woude anders keren / Dant die edele wise clerc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Des si ne weten groet no clene / Dat dichten ende dat scriven</t>
+          <t>Dus selen clercken sijn die leren / Die hem ter wijsheyt willen keren</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>daar zonder ik nimmer ne zijn / in dicht niet dat weten wel</t>
+          <t>een woord niet willen anders keren / dan het die edel wijs klerk</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>des zij ne weten groot noch klein / dat dicht en dat schrijven</t>
+          <t>dus zullen klerk zijn die leren / die hij ter wijsheid willen keren</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2952,31 +2952,31 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>0.5858190111720488</v>
+        <v>0.5765624050363991</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hy es Vader gebenedijt / Des Soens daer ghi moeder af sijt</t>
+          <t>Dat God ende ghi allene / Enen sone hebt gemene</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Na sinen wille gheschie mi / Sijn name si ghebenedijt</t>
+          <t>Es dat di wise menen / Wildi als een wijs man leven</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>hij zijn vader benedijen / de zoens daar gij moeder af zijn</t>
+          <t>dat NOU-P en gij alleen / een zoon hebben menen</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>na zijn wil geschieden ik / zijn naam zij benedijen</t>
+          <t>zijn dat du wijze menen / willen gij als een wijs man leven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2992,31 +2992,31 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>0.5867754515385348</v>
+        <v>0.5828871194908481</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dat God ende ghi allene / Enen sone hebt gemene</t>
+          <t>Anders dan dat ic niet en woude / Dat dese edele leringe soude</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Es dat di wise menen / Wildi als een wijs man leven</t>
+          <t>Dats dat nieman spreken en soude / Daer men niet horen en woude</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>dat NOU-P en gij alleen / een zoon hebben menen</t>
+          <t>anders dan dat ik niet ne willen / dat deze edel lering zullen</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>zijn dat du wijze menen / willen gij als een wijs man leven</t>
+          <t>dat zijn dat niemand spreken ne zullen / daar men niet horen ne willen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3032,31 +3032,31 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>0.5879080567681939</v>
+        <v>0.5833259931888619</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dat en dedic omme gene dinc / Anders dan dat ic niet en woude</t>
+          <t>Enen sone hebt gemene / Hy es Vader gebenedijt</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ere doghet ende alle goet / Gheen dinc en es soeter dan</t>
+          <t>Na sinen wille gheschie mi / Sijn name si ghebenedijt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>dat ne doen ik om geen ding / anders dan dat ik niet ne willen</t>
+          <t>een zoon hebben menen / hij zijn vader benedijen</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>een deugd en al goed / geen ding ne zijn zoet dan</t>
+          <t>na zijn wil geschieden ik / zijn naam zij benedijen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3072,31 +3072,31 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>0.590538227530414</v>
+        <v>0.5834907239813109</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>111</v>
+        <v>186</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Want dese bouc hevet in / Der warelt fundament ende beghin</t>
+          <t>Vander edelre Godheit / Daer by sy es ghevoeget scone</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nu hoert hier dat beghin / DIt boec beghint aldus</t>
+          <t>In die overste godheyde / Daer hi seker waer aen seyde</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>want deze boek hebben in / de wereld fundament en begin</t>
+          <t>van de edel godheid / daar bij zij zijn voegen schoon</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>nu hoeren hier dat begin / dit boek beginnen aldus</t>
+          <t>in die overst godheid / daar hij zeker waar aan zeggen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3112,31 +3112,31 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>0.5908853239641604</v>
+        <v>0.5835421510135741</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Enen sone hebt gemene / Hy es Vader gebenedijt</t>
+          <t>Want dese bouc hevet in / Der warelt fundament ende beghin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Na sinen wille gheschie mi / Sijn name si ghebenedijt</t>
+          <t>Nu hoert hier dat beghin / DIt boec beghint aldus</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>een zoon hebben menen / hij zijn vader benedijen</t>
+          <t>want deze boek hebben in / de wereld fundament en begin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>na zijn wil geschieden ik / zijn naam zij benedijen</t>
+          <t>nu hoeren hier dat begin / dit boek beginnen aldus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3152,31 +3152,31 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>0.5911472027006077</v>
+        <v>0.5838011611188951</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ende staet my in staden / Voer des Vaders Sone van hemelrike</t>
+          <t>Niet toe gebringen en can / Het es te swaer elcken man</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Om dat si hem in daden / Ende in rade soude staen in staden</t>
+          <t>Ende groet voerdeel elken man / Diet te poente gheraken can</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>en staan ik in stade / voor de vader zoon van hemelrijk</t>
+          <t>niet toegespreken gebrengen ne kunnen / het zijn te zwaar elk man</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>om dat zij hij in daad / en in raad zullen staan in stade</t>
+          <t>en groot voordeel elk man / die het te punt geraken kunnen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3192,31 +3192,31 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>0.5911553277280382</v>
+        <v>0.5874169337343528</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vander edelre Godheit / Daer by sy es ghevoeget scone</t>
+          <t>Hout voor eenen vont / Die beter es menichfout</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>In die overste godheyde / Daer hi seker waer aen seyde</t>
+          <t>Dan vele rijcheden sijn / Gratie es beter menechfout</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>van de edel godheid / daar bij zij zijn voegen schoon</t>
+          <t>hout voor een vont / die goed zijn menigvout</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>in die overst godheid / daar hij zeker waar aan zeggen</t>
+          <t>dan veel rijkheid zijn / gratie zijn goed menigvout</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3232,31 +3232,31 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>0.5929123505625795</v>
+        <v>0.5887804500620035</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Anders dan dat ic niet en woude / Dat dese edele leringe soude</t>
+          <t>Ende staet my in staden / Voer des Vaders Sone van hemelrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dats dat nieman spreken en soude / Daer men niet horen en woude</t>
+          <t>Om dat si hem in daden / Ende in rade soude staen in staden</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>anders dan dat ik niet ne willen / dat deze edel lering zullen</t>
+          <t>en staan ik in stade / voor de vader zoon van hemelrijk</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>dat zijn dat niemand spreken ne zullen / daar men niet horen ne willen</t>
+          <t>om dat zij hij in daad / en in raad zullen staan in stade</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3272,31 +3272,31 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>0.5932580545124319</v>
+        <v>0.5888959469520156</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hout voor eenen vont / Die beter es menichfout</t>
+          <t>Dat en dedic omme gene dinc / Anders dan dat ic niet en woude</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dan vele rijcheden sijn / Gratie es beter menechfout</t>
+          <t>Ere doghet ende alle goet / Gheen dinc en es soeter dan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>hout voor een vont / die goed zijn menigvout</t>
+          <t>dat ne doen ik om geen ding / anders dan dat ik niet ne willen</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>dan veel rijkheid zijn / gratie zijn goed menigvout</t>
+          <t>een deugd en al goed / geen ding ne zijn zoet dan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3312,31 +3312,31 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>0.5949224080697758</v>
+        <v>0.5904666617509186</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dicke hebbic die gene bescouden / Die hem ane die boeke houden</t>
+          <t>Waer of wi ons zouden hoeden / Die Sydrac leerde die vroede</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Daer om hebt liever den vrient / Die u bescelt als ghijs verdient</t>
+          <t>Versuumt hebbe so moghen wi / Ons een anderwerf hoeden</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>dik hebben ik die geen beschelden / die hij aan die beuk houden</t>
+          <t>waar af wij ons zullen hoeden / die sidrac leren die vroed</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>daar om hebben lief de vriend / die u beschelden als gij dat verdienen</t>
+          <t>verzuimen hebben zo mogen wij / ons een anderwerf hoeden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3352,31 +3352,31 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>0.5959719581660339</v>
+        <v>0.59072983707008</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Niet toe gebringen en can / Het es te swaer elcken man</t>
+          <t>Dat haer niet en es ontseit / Vander edelre Godheit</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ende groet voerdeel elken man / Diet te poente gheraken can</t>
+          <t>Datter luttel es gheset / In die overste godheyde</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>niet toegespreken gebrengen ne kunnen / het zijn te zwaar elk man</t>
+          <t>dat zij niet ne zijn ontzeggen / van de edel godheid</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>en groot voordeel elk man / die het te punt geraken kunnen</t>
+          <t>dat er luttel zijn zetten / in die overst godheid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3392,31 +3392,31 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>0.5985022121902011</v>
+        <v>0.5923242538632343</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dat haer niet en es ontseit / Vander edelre Godheit</t>
+          <t>Daer sonder ic nemmeer en ben / In dichte niet dat weet wale</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Datter luttel es gheset / In die overste godheyde</t>
+          <t>Des si ne weten groet no clene / Dat dichten ende dat scriven</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>dat zij niet ne zijn ontzeggen / van de edel godheid</t>
+          <t>daar zonder ik nimmer ne zijn / in dicht niet dat weten wel</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>dat er luttel zijn zetten / in die overst godheid</t>
+          <t>des zij ne weten groot noch klein / dat dicht en dat schrijven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3432,7 +3432,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>0.5986697424942702</v>
+        <v>0.5926290106294858</v>
       </c>
     </row>
     <row r="76">
@@ -3472,31 +3472,31 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>0.5987013242322758</v>
+        <v>0.5940928249658965</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Waer of wi ons zouden hoeden / Die Sydrac leerde die vroede</t>
+          <t>Soe hy alre gelijcxt can / Dit sal van rechte sijn sine sede</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Versuumt hebbe so moghen wi / Ons een anderwerf hoeden</t>
+          <t>Can ommate ghierechede / Toe bringhen hets haer sede</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>waar af wij ons zullen hoeden / die sidrac leren die vroed</t>
+          <t>zo hij al gelijk kunnen / dit zullen van rechte zijn zijn zede</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>verzuimen hebben zo mogen wij / ons een anderwerf hoeden</t>
+          <t>kunnen ommate gierigheid / toegespreken brengen het zijn haar zede</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3512,31 +3512,31 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
-        <v>0.5988594851199844</v>
+        <v>0.5954805991876202</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>47</v>
+        <v>198</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Soe quam my een boec ter hant / Daer ic in bescreven vant</t>
+          <t>Want ict niewer omme dede / Dan omme gemene zalichede</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Men vint voer waer bescreven / Daer vele liede sijn dat daer</t>
+          <t>Sonder sake voer waer gheseyt / Maer al om uwe salicheyt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>zo komen ik een boek ter hand / daar ik in beschrijven vinden</t>
+          <t>want ik het niewer om doen / dan om gemeen zaligheid</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>men vinden voor waar beschrijven / daar veel lieden zijn dat daar</t>
+          <t>zonder sake voor waar zeggen / maar al om uw zaligheid</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3552,31 +3552,31 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>0.6011562580560424</v>
+        <v>0.5968636176952182</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Soe hy alre gelijcxt can / Dit sal van rechte sijn sine sede</t>
+          <t>Dicke hebbic die gene bescouden / Die hem ane die boeke houden</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Can ommate ghierechede / Toe bringhen hets haer sede</t>
+          <t>Daer om hebt liever den vrient / Die u bescelt als ghijs verdient</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>zo hij al gelijk kunnen / dit zullen van rechte zijn zijn zede</t>
+          <t>dik hebben ik die geen beschelden / die hij aan die beuk houden</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>kunnen ommate gierigheid / toegespreken brengen het zijn haar zede</t>
+          <t>daar om hebben lief de vriend / die u beschelden als gij dat verdienen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3592,31 +3592,31 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>0.6014806804815976</v>
+        <v>0.5969767536217601</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>36</v>
+        <v>203</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Omme dat wy in dit leven / Dat overlijt soe cortelike</t>
+          <t>Die desen bouc selen scauwen / Dat sij Gode bidden vor mi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paulus seget in ene stede / Al dat ons in dit leven</t>
+          <t>Alsic u sal visieren / Dat beste besette als ic scouwe</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>om dat wij in dit leven / dat overlijd zo kortelijk</t>
+          <t>die deze boek zullen schouwen / dat zij NOU-P bidden voor ik</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NOU-P zeggen in een stede / al dat ons in dit leven</t>
+          <t>als ik u zullen viseren / dat goed bezetten als ik schouwen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3632,31 +3632,31 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
-        <v>0.6028221577139343</v>
+        <v>0.5974076999445764</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dat sij Gode bidden vor mi / Dat hi mijns genadich sij</t>
+          <t>Soe quam my een boec ter hant / Daer ic in bescreven vant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MElibeus antworde nu / Vrouwe segt mi ic bids u</t>
+          <t>Men vint voer waer bescreven / Daer vele liede sijn dat daer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>dat zij NOU-P bidden voor ik / dat hij ik genadig zijn</t>
+          <t>zo komen ik een boek ter hand / daar ik in beschrijven vinden</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NOU-P antwoorden nu / vrouwe zeggen ik ik bidden dat u</t>
+          <t>men vinden voor waar beschrijven / daar veel lieden zijn dat daar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3672,31 +3672,31 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
-        <v>0.6029016331368855</v>
+        <v>0.5986438311547886</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Die desen bouc selen scauwen / Dat sij Gode bidden vor mi</t>
+          <t>Voer des Vaders Sone van hemelrike / Dien ghi droecht menschelike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Alsic u sal visieren / Dat beste besette als ic scouwe</t>
+          <t>Want mesdoen es menschelijc / Maer daer in bliven es duvelijc</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>die deze boek zullen schouwen / dat zij NOU-P bidden voor ik</t>
+          <t>voor de vader zoon van hemelrijk / dat gij dragen menselijk</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>als ik u zullen viseren / dat goed bezetten als ik schouwen</t>
+          <t>want misdoen zijn menselijk / maar daar in blijven zijn duivellijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3712,31 +3712,31 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
-        <v>0.6048362884713672</v>
+        <v>0.6000833541585358</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Want ict niewer omme dede / Dan omme gemene zalichede</t>
+          <t>Die God alsoe hadde vercoren / Dat hijt al wiste te voren</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sonder sake voer waer gheseyt / Maer al om uwe salicheyt</t>
+          <t>Daer die Gods Sone vercoren / Ute woude sijn gheboren</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>want ik het niewer om doen / dan om gemeen zaligheid</t>
+          <t>die NOU-P alzo hebben verkiezen / dat hij het al wissen te voren</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>zonder sake voor waar zeggen / maar al om uw zaligheid</t>
+          <t>daar die NOU-P zoon verkiezen / uit het willen zijn geboren</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3752,31 +3752,31 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>0.605867394359094</v>
+        <v>0.6010488715889238</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Die God alsoe hadde vercoren / Dat hijt al wiste te voren</t>
+          <t>Hondertfout van lone / Te Antwerpen daer ic wone</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Daer die Gods Sone vercoren / Ute woude sijn gheboren</t>
+          <t>Sonder mi en moghedi doen niet / Al t Andwerpen daer ic wone</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>die NOU-P alzo hebben verkiezen / dat hij het al wissen te voren</t>
+          <t>honderdfout van loon / te NOU-P daar ik wonen</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>daar die NOU-P zoon verkiezen / uit het willen zijn geboren</t>
+          <t>zonder ik ne mogen gij doen niet / al het antwerpen daar ik wonen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3792,31 +3792,31 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>0.6059562723854748</v>
+        <v>0.6019154762260757</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hondertfout van lone / Te Antwerpen daer ic wone</t>
+          <t>Van vagheviere ende van paradise mede / Ende oerbare leringhe in menigher stede</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sonder mi en moghedi doen niet / Al t Andwerpen daer ic wone</t>
+          <t>Van volke ende van machte mede / Ende dies ghelijc in die stede</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>honderdfout van loon / te NOU-P daar ik wonen</t>
+          <t>van vagevuur en van paradijs mede / en oorbaar lering in menig stede</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>zonder ik ne mogen gij doen niet / al het antwerpen daar ik wonen</t>
+          <t>van volk en van macht mede / en dies gelijk in die stede</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3832,31 +3832,31 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>0.6074212084183458</v>
+        <v>0.6024830206849604</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>172</v>
+        <v>36</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Seker hy es herde sot / Ende vele meer dan ontsint</t>
+          <t>Omme dat wy in dit leven / Dat overlijt soe cortelike</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Want die sotte sijts gewes / En minnen niet dan dat sot es</t>
+          <t>Paulus seget in ene stede / Al dat ons in dit leven</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>zeker hij zijn hard zot / en veel meer dan ontzinnen</t>
+          <t>om dat wij in dit leven / dat overlijd zo kortelijk</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>want die zot zijn het gewis / ne minnen niet dan dat zot zijn</t>
+          <t>NOU-P zeggen in een stede / al dat ons in dit leven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3872,31 +3872,31 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>0.6083996716007776</v>
+        <v>0.6033275859573243</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Voer des Vaders Sone van hemelrike / Dien ghi droecht menschelike</t>
+          <t>Dan der werelt ydelheit / Ende leggen die boeke onder voet</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Want mesdoen es menschelijc / Maer daer in bliven es duvelijc</t>
+          <t>Dat al u dinc es ijdelheyt / Ende al dat begherden u oghen</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>voor de vader zoon van hemelrijk / dat gij dragen menselijk</t>
+          <t>dan de wereld ijdelheid / en leggen die beuk onder voet</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>want misdoen zijn menselijk / maar daar in blijven zijn duivellijk</t>
+          <t>dat al u ding zijn ijdelheid / en al dat begerden u oog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3912,31 +3912,31 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>0.6096269875646431</v>
+        <v>0.6046363623154519</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Want sy den tyt verliesen / Die nemmermeer no wijf no man</t>
+          <t>Dat sij Gode bidden vor mi / Dat hi mijns genadich sij</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Noch u niet noch andren man / Dien tgherechte niet gaet an</t>
+          <t>MElibeus antworde nu / Vrouwe segt mi ic bids u</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>want zij de tijd verliezen / die nimmermeer noch wijf noch man</t>
+          <t>dat zij NOU-P bidden voor ik / dat hij ik genadig zijn</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>noch u niet noch ander man / dat het gerecht niet gaan onnen</t>
+          <t>NOU-P antwoorden nu / vrouwe zeggen ik ik bidden dat u</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3952,31 +3952,31 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>0.6096749313351683</v>
+        <v>0.6048551895512805</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Die Sydrac leerde die vroede / Eenen onghelovighen coninc</t>
+          <t>Daer sy clene profijt inne leren / Alsoe sijn geesten vanden heren</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Die oude moet oec vroeder wesen / Die ane vele lieden heeft gheleert</t>
+          <t>Ende altoes leren hier ende daer / Dus selen clercken sijn die leren</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>die sidrac leren die vroed / een ongelovig koning</t>
+          <t>daar zij klein profijt in leren / alzo zijn geest van de heer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>die oude moeten ook vroed wezen / die aan veel lieden hebben leren</t>
+          <t>en altoos leren hier en daar / dus zullen klerk zijn die leren</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3992,31 +3992,31 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>0.611793004384106</v>
+        <v>0.6082844590716232</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dan der werelt ydelheit / Ende leggen die boeke onder voet</t>
+          <t>Den Dietscen lieden verholen wesen / Die geen Walsch en connen lesen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dat al u dinc es ijdelheyt / Ende al dat begherden u oghen</t>
+          <t>Die alle die loye die wesen / Binnen ende buten conste lesen</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>dan de wereld ijdelheid / en leggen die beuk onder voet</t>
+          <t>de Diets lieden verhelen wezen / die geen Waals ne kunnen lezen</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>dat al u ding zijn ijdelheid / en al dat begerden u oog</t>
+          <t>die al die looi die wezen / binnen en buiten kunnen lezen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4032,31 +4032,31 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>0.6127071765077482</v>
+        <v>0.6085266811133556</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Van vagheviere ende van paradise mede / Ende oerbare leringhe in menigher stede</t>
+          <t>Dat ic dit werc ierst ane ginc / Dat en dedic omme gene dinc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Van volke ende van machte mede / Ende dies ghelijc in die stede</t>
+          <t>Goeden vrouwen prijs gheeft / Hi seghet dat gheen dinc en gheyt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>van vagevuur en van paradijs mede / en oorbaar lering in menig stede</t>
+          <t>dat ik dit werk eerst eindigen gaan / dat ne doen ik om geen ding</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>van volk en van macht mede / en dies gelijk in die stede</t>
+          <t>goed vrouw prijs geven / hij zeggen dat geen ding ne gaan</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4072,31 +4072,31 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>0.6135680483813325</v>
+        <v>0.6089992278732943</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>4</v>
+        <v>174</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alsoe sijn geesten vanden heren / Van Pertelpeuse van Amedase</t>
+          <t>Die dese vrouwe niet en mint / Die de Vader alsoe minde</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Maer den gheest suldi gheloven / Dien God onse Here seynt van boven</t>
+          <t>Dies maect ons Paulus vroet / Om dat die goede doghet mint</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>alzo zijn geest van de heer / van partelpeuze van NOU-P</t>
+          <t>die deze vrouwe niet ne minnen / die de vader alzo minnen</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>maar de geest zullen gij geloven / dat NOU-P ons NOU-P zenden van boven</t>
+          <t>dies maken ons NOU-P vroed / om dat die goed deugd minnen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4112,31 +4112,31 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>0.6142682614104882</v>
+        <v>0.6094500741747484</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dat ic dit werc ierst ane ginc / Dat en dedic omme gene dinc</t>
+          <t>Seker hy es herde sot / Ende vele meer dan ontsint</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Goeden vrouwen prijs gheeft / Hi seghet dat gheen dinc en gheyt</t>
+          <t>Want die sotte sijts gewes / En minnen niet dan dat sot es</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>dat ik dit werk eerst eindigen gaan / dat ne doen ik om geen ding</t>
+          <t>zeker hij zijn hard zot / en veel meer dan ontzinnen</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>goed vrouw prijs geven / hij zeggen dat geen ding ne gaan</t>
+          <t>want die zot zijn het gewis / ne minnen niet dan dat zot zijn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4152,31 +4152,31 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>0.6143169853742956</v>
+        <v>0.6098098385554384</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dus quamen in hare scone / Beide die heilege Geest ende die Sone</t>
+          <t>Want sy den tyt verliesen / Die nemmermeer no wijf no man</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dat maect in hem een leven / Dan wercter die heylighe Gheest inne</t>
+          <t>Noch u niet noch andren man / Dien tgherechte niet gaet an</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>dus komen in haar scone / beide die heilig geest en die zoon</t>
+          <t>want zij de tijd verliezen / die nimmermeer noch wijf noch man</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>dat maken in hij een leven / dan werkt die heilig geest in</t>
+          <t>noch u niet noch ander man / dat het gerecht niet gaan onnen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4192,31 +4192,31 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>0.6145755925270699</v>
+        <v>0.6101975851997109</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Die dese vrouwe niet en mint / Die de Vader alsoe minde</t>
+          <t>Die Sydrac leerde die vroede / Eenen onghelovighen coninc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dies maect ons Paulus vroet / Om dat die goede doghet mint</t>
+          <t>Die oude moet oec vroeder wesen / Die ane vele lieden heeft gheleert</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>die deze vrouwe niet ne minnen / die de vader alzo minnen</t>
+          <t>die sidrac leren die vroed / een ongelovig koning</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>dies maken ons NOU-P vroed / om dat die goed deugd minnen</t>
+          <t>die oude moeten ook vroed wezen / die aan veel lieden hebben leren</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4232,31 +4232,31 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>0.6174798214995543</v>
+        <v>0.610325247812363</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ende die goede vrucht laten staen / Die goet sijn ende van smake soete</t>
+          <t>Dien ghi droecht menschelike / O Maria reine vat</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sydrac seyt die meester goet / Staet altoes na name goet</t>
+          <t>Want mesdoen es menschelijc / Maer daer in bliven es duvelijc</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>en die goed vrucht laten staan / die goed zijn en van smaak zoet</t>
+          <t>dat gij dragen menselijk / o NOU-P rein vat</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NOU-P zeggen die meester goed / staan altoos na naam goed</t>
+          <t>want misdoen zijn menselijk / maar daar in blijven zijn duivellijk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4272,31 +4272,31 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>0.6184268932332514</v>
+        <v>0.6141731305028376</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>170</v>
+        <v>24</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Des Soens daer ghi moeder af sijt / Ende die selve Sone es God</t>
+          <t>Ende die goede vrucht laten staen / Die goet sijn ende van smake soete</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>En droeft sprac hi in gheenre tijt / Om dat ghi uwes soens quite sijt</t>
+          <t>Sydrac seyt die meester goet / Staet altoes na name goet</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>de zoens daar gij moeder af zijn / en die zelf zoon zijn NOU-P</t>
+          <t>en die goed vrucht laten staan / die goed zijn en van smaak zoet</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ne droefd spreken hij in gene tijd / om dat gij u zoens kwijt zijn</t>
+          <t>NOU-P zeggen die meester goed / staan altoos na naam goed</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4312,31 +4312,31 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>0.6187556297338704</v>
+        <v>0.6159029000804439</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Daer sy clene profijt inne leren / Alsoe sijn geesten vanden heren</t>
+          <t>My dunct dat sy zere riesen / Want sy den tyt verliesen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ende altoes leren hier ende daer / Dus selen clercken sijn die leren</t>
+          <t>Met jonghen sotten riesen / Die u de wrake in bliesen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>daar zij klein profijt in leren / alzo zijn geest van de heer</t>
+          <t>ik dunken dat zij zeer riezen / want zij de tijd verliezen</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>en altoos leren hier en daar / dus zullen klerk zijn die leren</t>
+          <t>met jong zot riezen / die u de wrake innen blazen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4352,31 +4352,31 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
-        <v>0.61920853924352</v>
+        <v>0.6172022253347875</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Den Dietscen lieden verholen wesen / Die geen Walsch en connen lesen</t>
+          <t>Het es te swaer elcken man / Ende oec some ander dinc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Die alle die loye die wesen / Binnen ende buten conste lesen</t>
+          <t>Ende den mannen sonderlinghe / Want het sijn wijfs dinghe</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>de Diets lieden verhelen wezen / die geen Waals ne kunnen lezen</t>
+          <t>het zijn te zwaar elk man / en ook som ander ding</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>die al die looi die wezen / binnen en buiten kunnen lezen</t>
+          <t>en de man zonderling / want het zijn wijf ding</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4392,31 +4392,31 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
-        <v>0.6204867890279164</v>
+        <v>0.6189100427950966</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dien ghi droecht menschelike / O Maria reine vat</t>
+          <t>Alsoe sijn geesten vanden heren / Van Pertelpeuse van Amedase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Want mesdoen es menschelijc / Maer daer in bliven es duvelijc</t>
+          <t>Maer den gheest suldi gheloven / Dien God onse Here seynt van boven</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>dat gij dragen menselijk / o NOU-P rein vat</t>
+          <t>alzo zijn geest van de heer / van partelpeuze van NOU-P</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>want misdoen zijn menselijk / maar daar in blijven zijn duivellijk</t>
+          <t>maar de geest zullen gij geloven / dat NOU-P ons NOU-P zenden van boven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4432,31 +4432,31 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
-        <v>0.6230938469479654</v>
+        <v>0.6193632834578191</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Het es te swaer elcken man / Ende oec some ander dinc</t>
+          <t>Des Soens daer ghi moeder af sijt / Ende die selve Sone es God</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ende den mannen sonderlinghe / Want het sijn wijfs dinghe</t>
+          <t>En droeft sprac hi in gheenre tijt / Om dat ghi uwes soens quite sijt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>het zijn te zwaar elk man / en ook som ander ding</t>
+          <t>de zoens daar gij moeder af zijn / en die zelf zoon zijn NOU-P</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>en de man zonderling / want het zijn wijf ding</t>
+          <t>ne droefd spreken hij in gene tijd / om dat gij u zoens kwijt zijn</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4472,31 +4472,31 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>0.6240248069058557</v>
+        <v>0.6204977424695739</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Vele duechden ende wijsheden / Ende leringe van goeden seden</t>
+          <t>Dat hijt al wiste te voren / Dat in de werelt soude gevallen</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wijsheyt breect vele sorghen / Wijsheyt es niet verborghen</t>
+          <t>Mettien dat si met allen / Tuwer wille sijn ghevallen</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>veel deugd en wijsheid / en lering van goed zede</t>
+          <t>dat hij het al wissen te voren / dat in de wereld zullen vallen</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>wijsheid breken veel zorg / wijsheid zijn niet verborgen</t>
+          <t>mettien dat zij met al / te uw wil zijn vallen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4512,31 +4512,31 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>0.624345429169037</v>
+        <v>0.6207606717853772</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>My dunct dat sy zere riesen / Want sy den tyt verliesen</t>
+          <t>Dus quamen in hare scone / Beide die heilege Geest ende die Sone</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Met jonghen sotten riesen / Die u de wrake in bliesen</t>
+          <t>Dat maect in hem een leven / Dan wercter die heylighe Gheest inne</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ik dunken dat zij zeer riezen / want zij de tijd verliezen</t>
+          <t>dus komen in haar scone / beide die heilig geest en die zoon</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>met jong zot riezen / die u de wrake innen blazen</t>
+          <t>dat maken in hij een leven / dan werkt die heilig geest in</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4552,31 +4552,31 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>0.624516259767441</v>
+        <v>0.6218734681156444</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>In dichte niet dat weet wale / Dien boec ute altemale</t>
+          <t>Vele duechden ende wijsheden / Ende leringe van goeden seden</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Des si ne weten groet no clene / Dat dichten ende dat scriven</t>
+          <t>Wijsheyt breect vele sorghen / Wijsheyt es niet verborghen</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>in dicht niet dat weten wel / dat boek uit altemaal</t>
+          <t>veel deugd en wijsheid / en lering van goed zede</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>des zij ne weten groot noch klein / dat dicht en dat schrijven</t>
+          <t>wijsheid breken veel zorg / wijsheid zijn niet verborgen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4592,7 +4592,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
-        <v>0.6255232023237424</v>
+        <v>0.6250583559962595</v>
       </c>
     </row>
     <row r="105">
@@ -4632,31 +4632,31 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
-        <v>0.6267414835850107</v>
+        <v>0.6251250539930759</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hy en deder toe noch af / Anders dant dauctor ute gaf</t>
+          <t>Ende XLVII daer naer / Dese Sydrac was van Gode vercoren</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Men mochter so haestelijc toe gaen / Men souder grote scade af ontfaen</t>
+          <t>Daer die Gods Sone vercoren / Ute woude sijn gheboren</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>hij ne doen er toegespreken nog afhebben hij / anders dan het de autor uiten geven</t>
+          <t>en zevenenveertig daar naar / deze sidrac zijn van NOU-P verkiezen</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>men mogen er zo haastelijk toegespreken gaan / men zullen er groot schade afhebben hij ontvangen</t>
+          <t>daar die NOU-P zoon verkiezen / uit het willen zijn geboren</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4672,31 +4672,31 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>0.6270856091012</v>
+        <v>0.6268795492854364</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dat hijt al wiste te voren / Dat in de werelt soude gevallen</t>
+          <t>Want ic hope sonder waen / Dat sy selen daer omme bedi</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mettien dat si met allen / Tuwer wille sijn ghevallen</t>
+          <t>So dat ic u sal sonder waen / Vergheven dat ghi mi hebt mesdaen</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>dat hij het al wissen te voren / dat in de wereld zullen vallen</t>
+          <t>want ik hopen zonder waan / dat zij zullen daar om bedie</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>mettien dat zij met al / te uw wil zijn vallen</t>
+          <t>zo dat ik u zullen zonder waan / vergeven dat gij ik hebben misdoen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4712,31 +4712,31 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>0.6280835661650692</v>
+        <v>0.6271852248395348</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Want ic hope sonder waen / Dat sy selen daer omme bedi</t>
+          <t>Hadde bekeert te sinen ghebode / Dit was naer Noe VIIIc iaer</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>So dat ic u sal sonder waen / Vergheven dat ghi mi hebt mesdaen</t>
+          <t>Ghelijc sinen scepper sinen God / Daer hi af hadde sijn ghebot</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>want ik hopen zonder waan / dat zij zullen daar om bedie</t>
+          <t>hebben bekeren te zijn gebod / dit zijn naar NOU-P achttiende jaar</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>zo dat ik u zullen zonder waan / vergeven dat gij ik hebben misdoen</t>
+          <t>gelijk zijn schepper zijn NOU-P / daar hij af hebben zijn gebod</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4752,7 +4752,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>0.6281505177005046</v>
+        <v>0.6298386827546147</v>
       </c>
     </row>
     <row r="109">
@@ -4792,31 +4792,31 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>0.6285008981899367</v>
+        <v>0.6300565932885596</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Beide die heilege Geest ende die Sone / Die een God sijn metten Vader</t>
+          <t>Anders dant dauctor ute gaf / Die anders doen sy doen quaet</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dat maect in hem een leven / Dan wercter die heylighe Gheest inne</t>
+          <t>Dan diet al prijst dat ghi doet / Weder het si quaet of goet</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>beide die heilig geest en die zoon / die een god zijn met de vader</t>
+          <t>anders dan het de autor uiten geven / die anders doen zij doen kwaad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>dat maken in hij een leven / dan werkt die heilig geest in</t>
+          <t>dan die het al prijzen dat gij doen / weder het zij kwaad of goed</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4832,31 +4832,31 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>0.6296809778341018</v>
+        <v>0.6315104113850619</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PROLOGHE / Dicke hebbic die gene bescouden</t>
+          <t>Hy en deder toe noch af / Anders dant dauctor ute gaf</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Daer om hebt liever den vrient / Die u bescelt als ghijs verdient</t>
+          <t>Men mochter so haestelijc toe gaen / Men souder grote scade af ontfaen</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>proloog / dik hebben ik die geen beschelden</t>
+          <t>hij ne doen er toegespreken nog afhebben hij / anders dan het de autor uiten geven</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>daar om hebben lief de vriend / die u beschelden als gij dat verdienen</t>
+          <t>men mogen er zo haastelijk toegespreken gaan / men zullen er groot schade afhebben hij ontvangen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4872,31 +4872,31 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>0.6296819447138791</v>
+        <v>0.6324699430473046</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ende XLVII daer naer / Dese Sydrac was van Gode vercoren</t>
+          <t>In dichte niet dat weet wale / Dien boec ute altemale</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Daer die Gods Sone vercoren / Ute woude sijn gheboren</t>
+          <t>Des si ne weten groet no clene / Dat dichten ende dat scriven</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>en zevenenveertig daar naar / deze sidrac zijn van NOU-P verkiezen</t>
+          <t>in dicht niet dat weten wel / dat boek uit altemaal</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>daar die NOU-P zoon verkiezen / uit het willen zijn geboren</t>
+          <t>des zij ne weten groot noch klein / dat dicht en dat schrijven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4912,31 +4912,31 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>0.6323819095606845</v>
+        <v>0.6325977991813161</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Anders dant dauctor ute gaf / Die anders doen sy doen quaet</t>
+          <t>PROLOGHE / Dicke hebbic die gene bescouden</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dan diet al prijst dat ghi doet / Weder het si quaet of goet</t>
+          <t>Daer om hebt liever den vrient / Die u bescelt als ghijs verdient</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>anders dan het de autor uiten geven / die anders doen zij doen kwaad</t>
+          <t>proloog / dik hebben ik die geen beschelden</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>dan die het al prijzen dat gij doen / weder het zij kwaad of goed</t>
+          <t>daar om hebben lief de vriend / die u beschelden als gij dat verdienen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4952,31 +4952,31 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>0.6333450019667167</v>
+        <v>0.6330032542865258</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ende de welke behouden zal sijn / Als God de warelt zal domen</t>
+          <t>Die sal den text leggen dan / Soe hy alre gelijcxt can</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sonder ontfermenesse sal hi / Oec ghedoemt werden daer bi</t>
+          <t>Die vele wilt connen ende luttel can / Bedrieghet meest hem selven dan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>en de welk behouden zullen zijn / als NOU-P de wereld zullen doemen</t>
+          <t>die zullen de tekst leggen dan / zo hij al gelijk kunnen</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>zonder ontfermenis zullen hij / ook doemen worden daar bij</t>
+          <t>die veel willen kunnen en luttel kunnen / bedriegen meest hij zelf dan</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4992,31 +4992,31 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>0.6369560289490039</v>
+        <v>0.6338521873486435</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hadde bekeert te sinen ghebode / Dit was naer Noe VIIIc iaer</t>
+          <t>Ende de welke behouden zal sijn / Als God de warelt zal domen</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ghelijc sinen scepper sinen God / Daer hi af hadde sijn ghebot</t>
+          <t>Sonder ontfermenesse sal hi / Oec ghedoemt werden daer bi</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>hebben bekeren te zijn gebod / dit zijn naar NOU-P achttiende jaar</t>
+          <t>en de welk behouden zullen zijn / als NOU-P de wereld zullen doemen</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>gelijk zijn schepper zijn NOU-P / daar hij af hebben zijn gebod</t>
+          <t>zonder ontfermenis zullen hij / ook doemen worden daar bij</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5032,31 +5032,31 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>0.6383347558507667</v>
+        <v>0.6353108836383852</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hebbic al gelaten uut / Nu hulpt my Goids bruit</t>
+          <t>Beide die heilege Geest ende die Sone / Die een God sijn metten Vader</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>En hebbic niet in mi / Al woudic al laten varen</t>
+          <t>Dat maect in hem een leven / Dan wercter die heylighe Gheest inne</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>hebben ik al laten uiten / nu helpen ik NOU-P bruid</t>
+          <t>beide die heilig geest en die zoon / die een god zijn met de vader</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ne hebben ik niet in ik / al willen ik al laten varen</t>
+          <t>dat maken in hij een leven / dan werkt die heilig geest in</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5072,31 +5072,31 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="n">
-        <v>0.6402142380972817</v>
+        <v>0.6373248816333325</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Als God de warelt zal domen / Ende hoe si ter bliscap sullen comen</t>
+          <t>Ende oerbare leringhe in menigher stede / Waer of wi ons zouden hoeden</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sonder ontfermenesse sal hi / Oec ghedoemt werden daer bi</t>
+          <t>Versuumt hebbe so moghen wi / Ons een anderwerf hoeden</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>als NOU-P de wereld zullen doemen / en hoe zij ter blijdschap zullen komen</t>
+          <t>en oorbaar lering in menig stede / waar af wij ons zullen hoeden</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>zonder ontfermenis zullen hij / ook doemen worden daar bij</t>
+          <t>verzuimen hebben zo mogen wij / ons een anderwerf hoeden</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5112,31 +5112,31 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>0.6407227311571893</v>
+        <v>0.6391302603345577</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Die boec daer icse ute trac / Es geheten die wise Sidrac</t>
+          <t>Dat hy inden Walsce lach / Omme dat ic van dier edelre leren</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wildi des boecx name weten / Melibeus sal hi heten</t>
+          <t>Ghemaect tote onse lere / Seneca seghet die here</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>die boek daar ik zij uit trekken / zijn heten die wijze NOU-P</t>
+          <t>dat hij in de wals lachen / om dat ik van die edel leer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>willen gij de boek naam weten / NOU-P zullen hij heten</t>
+          <t>maken tot ons leer / NOU-P zeggen die heer</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5152,31 +5152,31 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
-        <v>0.6435021762742581</v>
+        <v>0.6395080441182046</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Int latijn dichte als een clerc / Uten Grixe dat hy conste wale</t>
+          <t>Als God de warelt zal domen / Ende hoe si ter bliscap sullen comen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ende uten lereren also wale / Also dat latijn houdt in</t>
+          <t>Sonder ontfermenesse sal hi / Oec ghedoemt werden daer bi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>in het latijn dichten als een klerk / uit dat griks dat hij kunnen wel</t>
+          <t>als NOU-P de wereld zullen doemen / en hoe zij ter blijdschap zullen komen</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>en uit dat leraar alzo wel / alzo dat latijn houden innen</t>
+          <t>zonder ontfermenis zullen hij / ook doemen worden daar bij</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5192,7 +5192,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>0.6452499828681526</v>
+        <v>0.6396366708788166</v>
       </c>
     </row>
     <row r="120">
@@ -5232,31 +5232,31 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>0.646191206313889</v>
+        <v>0.6413416976262786</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Die sal den text leggen dan / Soe hy alre gelijcxt can</t>
+          <t>Die boec daer icse ute trac / Es geheten die wise Sidrac</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Die vele wilt connen ende luttel can / Bedrieghet meest hem selven dan</t>
+          <t>Wildi des boecx name weten / Melibeus sal hi heten</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>die zullen de tekst leggen dan / zo hij al gelijk kunnen</t>
+          <t>die boek daar ik zij uit trekken / zijn heten die wijze NOU-P</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>die veel willen kunnen en luttel kunnen / bedriegen meest hij zelf dan</t>
+          <t>willen gij de boek naam weten / NOU-P zullen hij heten</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5272,31 +5272,31 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
-        <v>0.6472924392383437</v>
+        <v>0.6458521287364231</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dat hy inden Walsce lach / Omme dat ic van dier edelre leren</t>
+          <t>Hebbic al gelaten uut / Nu hulpt my Goids bruit</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ghemaect tote onse lere / Seneca seghet die here</t>
+          <t>En hebbic niet in mi / Al woudic al laten varen</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>dat hij in de wals lachen / om dat ik van die edel leer</t>
+          <t>hebben ik al laten uiten / nu helpen ik NOU-P bruid</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>maken tot ons leer / NOU-P zeggen die heer</t>
+          <t>ne hebben ik niet in ik / al willen ik al laten varen</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5312,31 +5312,31 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>0.6481283362151802</v>
+        <v>0.6466719991527775</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ende oerbare leringhe in menigher stede / Waer of wi ons zouden hoeden</t>
+          <t>Int latijn dichte als een clerc / Uten Grixe dat hy conste wale</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Versuumt hebbe so moghen wi / Ons een anderwerf hoeden</t>
+          <t>Ende uten lereren also wale / Also dat latijn houdt in</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>en oorbaar lering in menig stede / waar af wij ons zullen hoeden</t>
+          <t>in het latijn dichten als een klerk / uit dat griks dat hij kunnen wel</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>verzuimen hebben zo mogen wij / ons een anderwerf hoeden</t>
+          <t>en uit dat leraar alzo wel / alzo dat latijn houden innen</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5352,31 +5352,31 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>0.6484666045541878</v>
+        <v>0.6473228067703345</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dat hi mijns genadich sij / Alst comt te minen laetsten stonden</t>
+          <t>Met dichtene minen sin / Daer sonder ic nemmeer en ben</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mijn here sal u sijn ghenadich / Daer en twifelt u niet an</t>
+          <t>Die niet rijp en hebben den sin / Daer en es niet dan kijnscheyt in</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>dat hij ik genadig zijn / als het komen te mijn laat stond</t>
+          <t>met dichten mijn zin / daar zonder ik nimmer ne zijn</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>mijn heer zullen u zijn genadig / daar ne twijfelen u niet aan</t>
+          <t>die niet rijp ne hebben de zin / daar ne zijn niet dan kinsheid en</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5392,31 +5392,31 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
-        <v>0.6486363837592783</v>
+        <v>0.6474958228036782</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dien boec ute altemale / Vanden cruden latic uut</t>
+          <t>Dat hi mijns genadich sij / Alst comt te minen laetsten stonden</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Uten loye decretale / Ende uten lereren also wale</t>
+          <t>Mijn here sal u sijn ghenadich / Daer en twifelt u niet an</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>dat boek uit altemaal / van de kruid laten ik uit</t>
+          <t>dat hij ik genadig zijn / als het komen te mijn laat stond</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>uit dat looi decretaal / en uit dat leraar alzo wel</t>
+          <t>mijn heer zullen u zijn genadig / daar ne twijfelen u niet aan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5432,31 +5432,31 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>0.6491443931500469</v>
+        <v>0.6476311365697948</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Es geheten die wise Sidrac / Na enen clerc wijs ende fijn</t>
+          <t>Hoe hem in die helle staet te sine / Van vagheviere ende van paradise mede</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Een wijs meester spreect aldus / Die men heet Alphontius</t>
+          <t>Die wilen in Troyen was / Van volke ende van machte mede</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>zijn heten die wijze NOU-P / na een klerk wijs en fijn</t>
+          <t>hoe hij in die hel staan te zijn / van vagevuur en van paradijs mede</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>een wijs meester spreken aldus / die men heten NOU-P</t>
+          <t>die wijlen in NOU-P zijn / van volk en van macht mede</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5472,31 +5472,31 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>0.6510044268333276</v>
+        <v>0.6491975478414633</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Omme dat ic die pine bestoet / Want die leringe die es goet</t>
+          <t>Dien boec ute altemale / Vanden cruden latic uut</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metter heyligher leringhen / Die de litteren uut gheven</t>
+          <t>Uten loye decretale / Ende uten lereren also wale</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>om dat ik die pijn bestaan / want die lering die zijn goed</t>
+          <t>dat boek uit altemaal / van de kruid laten ik uit</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>met de heilig lering / die de letter uiten geven</t>
+          <t>uit dat looi decretaal / en uit dat leraar alzo wel</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5512,31 +5512,31 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
-        <v>0.653824777182048</v>
+        <v>0.650256155245265</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dit boec was in Walsche bescreven / Sonder rime in slechte woert</t>
+          <t>Es geheten die wise Sidrac / Na enen clerc wijs ende fijn</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Oec bescrijft hi wel voerwaer / Dat hi dit boec maecte int jaer</t>
+          <t>Beter es een name goet en fijn / Dan vele rijcheden sijn</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>dit boek zijn in Waals beschrijven / zonder rijm in slecht woord</t>
+          <t>zijn heten die wijze NOU-P / na een klerk wijs en fijn</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ook beschrijven hij wel voorwaar / dat hij dit boek maken in het jaar</t>
+          <t>goed zijn een naam goed en fijn / dan veel rijkheid zijn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5552,31 +5552,31 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
-        <v>0.6541329244761025</v>
+        <v>0.6515140006727589</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>147</v>
+        <v>62</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Met dichtene minen sin / Daer sonder ic nemmeer en ben</t>
+          <t>Selve dichte in sijn werc / Want rime alsoe wijt vinden</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Die niet rijp en hebben den sin / Daer en es niet dan kijnscheyt in</t>
+          <t>Mesdoedi dat sal hi merken / Eest in worden of in werken</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>met dichten mijn zin / daar zonder ik nimmer ne zijn</t>
+          <t>zelf dichten in zijn werk / want rijm alzo wij het vinden</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>die niet rijp ne hebben de zin / daar ne zijn niet dan kinsheid en</t>
+          <t>misdoedi dat zullen hij merken / zijn het in woord of in werk</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5592,31 +5592,31 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="n">
-        <v>0.6579845573102296</v>
+        <v>0.6523769756943022</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Selve dichte in sijn werc / Want rime alsoe wijt vinden</t>
+          <t>Omme dat ic die pine bestoet / Want die leringe die es goet</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Mesdoedi dat sal hi merken / Eest in worden of in werken</t>
+          <t>Metter heyligher leringhen / Die de litteren uut gheven</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>zelf dichten in zijn werk / want rijm alzo wij het vinden</t>
+          <t>om dat ik die pijn bestaan / want die lering die zijn goed</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>misdoedi dat zullen hij merken / zijn het in woord of in werk</t>
+          <t>met de heilig lering / die de letter uiten geven</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5632,31 +5632,31 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="n">
-        <v>0.6582529507685728</v>
+        <v>0.6538571423865029</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Hoet metten achtersten zal gaen / Daer de warelt zal nemen fijn</t>
+          <t>Dit boec was in Walsche bescreven / Sonder rime in slechte woert</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Daer om en suldi hoet gaet / Haestelijc gheven no nemen raet</t>
+          <t>Oec bescrijft hi wel voerwaer / Dat hi dit boec maecte int jaer</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>hoe het met de achterste zullen gaan / daar de wereld zullen nemen fijn</t>
+          <t>dit boek zijn in Waals beschrijven / zonder rijm in slecht woord</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>daar om ne zullen gij hoe het gaan / haastelijk geven noch nemen raad</t>
+          <t>ook beschrijven hij wel voorwaar / dat hij dit boek maken in het jaar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5672,7 +5672,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
-        <v>0.658597973073376</v>
+        <v>0.6563998577245649</v>
       </c>
     </row>
     <row r="132">
@@ -5712,31 +5712,31 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
-        <v>0.6590546270096966</v>
+        <v>0.6569617239645864</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Hoe hem in die helle staet te sine / Van vagheviere ende van paradise mede</t>
+          <t>Uten Walsche in Dietsche spraken / Sonder rime alsoe ic sach</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Die wilen in Troyen was / Van volke ende van machte mede</t>
+          <t>Salomon seghet Soete spraken / Connen vele vriende maken</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>hoe hij in die hel staan te zijn / van vagevuur en van paradijs mede</t>
+          <t>uit dat Waals in Diets spraak / zonder rijm alzo ik zien</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>die wijlen in NOU-P zijn / van volk en van macht mede</t>
+          <t>NOU-P zeggen zoet spraak / kunnen veel vriend maken</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5752,31 +5752,31 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
-        <v>0.6597571255397465</v>
+        <v>0.6574652623417756</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ende oec ute Ebreusche tale / Hy en deder toe noch af</t>
+          <t>Hoet metten achtersten zal gaen / Daer de warelt zal nemen fijn</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Men mochter so haestelijc toe gaen / Men souder grote scade af ontfaen</t>
+          <t>Daer om en suldi hoet gaet / Haestelijc gheven no nemen raet</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>en ook uit Ebreus taal / hij ne doen er toegespreken nog afhebben hij</t>
+          <t>hoe het met de achterste zullen gaan / daar de wereld zullen nemen fijn</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>men mogen er zo haastelijk toegespreken gaan / men zullen er groot schade afhebben hij ontvangen</t>
+          <t>daar om ne zullen gij hoe het gaan / haastelijk geven noch nemen raad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5792,31 +5792,31 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
-        <v>0.6605450181762895</v>
+        <v>0.6588055179702524</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Macht sin ende ghesonde / Ende te levene zo langhe stonde</t>
+          <t>Dant die edele wise clerc / Selve dichte in sijn werc</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ghesonde der sielen ende den live / Al comen si uut enen wive</t>
+          <t>Mesdoedi dat sal hi merken / Eest in worden of in werken</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>macht zin en gezonde / en te leven zo lang stonde</t>
+          <t>dan het die edel wijs klerk / zelf dichten in zijn werk</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>gezonde de ziel en de lijf / al komen zij uit een wijf</t>
+          <t>misdoedi dat zullen hij merken / zijn het in woord of in werk</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5832,31 +5832,31 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
-        <v>0.6614144485190006</v>
+        <v>0.6589360306770833</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>211</v>
+        <v>64</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Doe men Gods iare noteerde / XIIIc XV ende drie</t>
+          <t>Doet dicke die materie winden / Anders danse die makere seide</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Int jaer na Gods gheboert / XIIIc XL ende twee</t>
+          <t>Hi sprac Die scalke rade vinden / Dat si op hem selven winden</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>toen men NOU-P jaar noteren / vierentwintig vijftien een drie</t>
+          <t>doen dik die materie winden / anders dans die maker zeggen</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>in het jaar na NOU-P geboorte / vierentwintig veertig een twee</t>
+          <t>hij spreken die schalk raad vinden / dat zij op hij zelf winden</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5872,31 +5872,31 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
-        <v>0.6620527239399135</v>
+        <v>0.6593779746133306</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dant die edele wise clerc / Selve dichte in sijn werc</t>
+          <t>Die liden doer enen bogaert / Die met vruchten sijn bewaert</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mesdoedi dat sal hi merken / Eest in worden of in werken</t>
+          <t>Dat die ghene wel es bewaert / Die vele vriende heeft in die vaert</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>dan het die edel wijs klerk / zelf dichten in zijn werk</t>
+          <t>die lijden door een boomgaard / die met vrucht zijn bewaren</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>misdoedi dat zullen hij merken / zijn het in woord of in werk</t>
+          <t>dat die gene wel zijn bewaren / die veel vriend hebben in die vaart</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5912,31 +5912,31 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
-        <v>0.663190824652508</v>
+        <v>0.6605192167584473</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Die liden doer enen bogaert / Die met vruchten sijn bewaert</t>
+          <t>Ende anders en hebben engene lere / Dan vechten ende vrouwen te minnen</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dat die ghene wel es bewaert / Die vele vriende heeft in die vaert</t>
+          <t>Dan te wesene sonder leren / Die derde wijsheyt des sijt vroet</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>die lijden door een boomgaard / die met vrucht zijn bewaren</t>
+          <t>en anders ne hebben negeen leer / dan vechten en vrouw te minnen</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>dat die gene wel zijn bewaren / die veel vriend hebben in die vaart</t>
+          <t>dan te wezen zonder leer / die derde wijsheid de zijn vroed</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5952,31 +5952,31 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
-        <v>0.6641594944615692</v>
+        <v>0.6614914366554758</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>54</v>
+        <v>202</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Doen werdic daer toe becoert / Dat ic dit boec woude maken</t>
+          <t>Ende ic bidde hem allen met trauwen / Die desen bouc selen scauwen</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maecte ic dit boexken scone / Wildi des boecx name weten</t>
+          <t>Alsic u sal visieren / Dat beste besette als ic scouwe</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>toen worden ik daar toe bekoren / dat ik dit boek willen maken</t>
+          <t>en ik bidden hij al met trouw / die deze boek zullen schouwen</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>maken ik dit boekje schoon / willen gij de boek naam weten</t>
+          <t>als ik u zullen viseren / dat goed bezetten als ik schouwen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5992,31 +5992,31 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
-        <v>0.6648540108621712</v>
+        <v>0.661888237728973</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Die ic hier na bescrive / Die boec daer icse ute trac</t>
+          <t>Macht sin ende ghesonde / Ende te levene zo langhe stonde</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Also bescreef hi selve dat / Oec bescrijft hi wel voerwaer</t>
+          <t>Ghesonde der sielen ende den live / Al comen si uut enen wive</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>die ik hier na beschrijven / die boek daar ik zij uit trekken</t>
+          <t>macht zin en gezonde / en te leven zo lang stonde</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>alzo beschrijven hij zelf dat / ook beschrijven hij wel voorwaar</t>
+          <t>gezonde de ziel en de lijf / al komen zij uit een wijf</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6032,31 +6032,31 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
-        <v>0.666385021491593</v>
+        <v>0.6618945631307136</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ende ic bidde hem allen met trauwen / Die desen bouc selen scauwen</t>
+          <t>Ende gheworpen in die pine / Hoe hem in die helle staet te sine</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Alsic u sal visieren / Dat beste besette als ic scouwe</t>
+          <t>Hem en behoert niet allene te sine / Doen nam hi al sonder pine</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>en ik bidden hij al met trouw / die deze boek zullen schouwen</t>
+          <t>en werpen in die pijn / hoe hij in die hel staan te zijn</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>als ik u zullen viseren / dat goed bezetten als ik schouwen</t>
+          <t>hij ne behoren niet alleen te zijn / toen nemen hij al zonder pijn</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6072,31 +6072,31 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
-        <v>0.6664684190745911</v>
+        <v>0.6633687114029092</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ende anders en hebben engene lere / Dan vechten ende vrouwen te minnen</t>
+          <t>Die ic hier na bescrive / Die boec daer icse ute trac</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dan te wesene sonder leren / Die derde wijsheyt des sijt vroet</t>
+          <t>Also bescreef hi selve dat / Oec bescrijft hi wel voerwaer</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>en anders ne hebben negeen leer / dan vechten en vrouw te minnen</t>
+          <t>die ik hier na beschrijven / die boek daar ik zij uit trekken</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>dan te wezen zonder leer / die derde wijsheid de zijn vroed</t>
+          <t>alzo beschrijven hij zelf dat / ook beschrijven hij wel voorwaar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6112,31 +6112,31 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
-        <v>0.6677957564452603</v>
+        <v>0.6642857937032132</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Uten Walsche in Dietsche spraken / Sonder rime alsoe ic sach</t>
+          <t>Ende oec ute Ebreusche tale / Hy en deder toe noch af</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Salomon seghet Soete spraken / Connen vele vriende maken</t>
+          <t>Men mochter so haestelijc toe gaen / Men souder grote scade af ontfaen</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>uit dat Waals in Diets spraak / zonder rijm alzo ik zien</t>
+          <t>en ook uit Ebreus taal / hij ne doen er toegespreken nog afhebben hij</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>NOU-P zeggen zoet spraak / kunnen veel vriend maken</t>
+          <t>men mogen er zo haastelijk toegespreken gaan / men zullen er groot schade afhebben hij ontvangen</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6152,31 +6152,31 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>0.6680289505647045</v>
+        <v>0.6657350927463699</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ende leringe van goeden seden / Ende hoe die mensce soude leven</t>
+          <t>Doe men Gods iare noteerde / XIIIc XV ende drie</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ende haer leringhe wel verstaen / Ende van allen ghewaghen</t>
+          <t>Int jaer na Gods gheboert / XIIIc XL ende twee</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>en lering van goed zede / en hoe die mens zullen leven</t>
+          <t>toen men NOU-P jaar noteren / vierentwintig vijftien een drie</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>en haar lering wel verstaan / en van al gewag</t>
+          <t>in het jaar na NOU-P geboorte / vierentwintig veertig een twee</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6192,31 +6192,31 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
-        <v>0.6688597513124962</v>
+        <v>0.6690946018444042</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Doet dicke die materie winden / Anders danse die makere seide</t>
+          <t>Ende netelen ende distelen plucken gaen / Ende die goede vrucht laten staen</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hi sprac Die scalke rade vinden / Dat si op hem selven winden</t>
+          <t>Ende met sinen wive gaen / Ende beyde in enen vleesche staen</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>doen dik die materie winden / anders dans die maker zeggen</t>
+          <t>en netelen en distel plukken gaan / en die goed vrucht laten staan</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>hij spreken die schalk raad vinden / dat zij op hij zelf winden</t>
+          <t>en met zijn wijf gaan / en beide in een vlees staan</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6232,31 +6232,31 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
-        <v>0.6700673182486312</v>
+        <v>0.6696837108210928</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dan vechten ende vrouwen te minnen / Ende lant ende stede ende borge te winnen</t>
+          <t>Ende leringe van goeden seden / Ende hoe die mensce soude leven</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Daer en es niet dan kijnscheyt in / Ende si minnen spade ende vroe</t>
+          <t>Die wile dat die mensche leeft / Also ons Seneca seghet</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>dan vechten en vrouw te minnen / en land en stede en borg te winnen</t>
+          <t>en lering van goed zede / en hoe die mens zullen leven</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>daar ne zijn niet dan kinsheid en / en zij minnen spa en vroe</t>
+          <t>die wijl dat die mens leven / alzo ons NOU-P zeggen</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6272,31 +6272,31 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
-        <v>0.6701451715574713</v>
+        <v>0.6699483292360424</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ende menich boec datmen mint / Daer men luttel orboers in vint</t>
+          <t>Doen werdic daer toe becoert / Dat ic dit boec woude maken</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ende meneghe wijsheit daer toe wet / Vindi in dit boec gheset</t>
+          <t>Maecte ic dit boexken scone / Wildi des boecx name weten</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>en menig boek dat men minnen / daar men luttel oorbaar in vinden</t>
+          <t>toen worden ik daar toe bekoren / dat ik dit boek willen maken</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>en menig wijsheid daar toe wetten / vinden gij in dit boek zetten</t>
+          <t>maken ik dit boekje schoon / willen gij de boek naam weten</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6312,31 +6312,31 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>0.670203538627168</v>
+        <v>0.6700340293248945</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ende lant ende stede ende borge te winnen / Daer anders niet inne en leit</t>
+          <t>Dan vechten ende vrouwen te minnen / Ende lant ende stede ende borge te winnen</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ende dat si aldaer ter stede / Haer borghen souden bringhen mede</t>
+          <t>Daer en es niet dan kijnscheyt in / Ende si minnen spade ende vroe</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>en land en stede en borg te winnen / daar anders niet in ne liggen</t>
+          <t>dan vechten en vrouw te minnen / en land en stede en borg te winnen</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>en dat zij aldaar ter stede / haar borg zullen brengen mede</t>
+          <t>daar ne zijn niet dan kinsheid en / en zij minnen spa en vroe</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6352,31 +6352,31 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
-        <v>0.6708158422337425</v>
+        <v>0.6709580141387816</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dat hi mi wille verlenen / Macht sin ende ghesonde</t>
+          <t>Ende minen zin also verclaerde / Dat ic dit werc met minen arbeide</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ghesonde der sielen ende den live / Al comen si uut enen wive</t>
+          <t>Dats al verloren arbeyt / Ic hebt u nu toe gheseyt</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>dat hij ik willen verlenen / macht zin en gezonde</t>
+          <t>en mijn zin alzo verklaren / dat ik dit werk met mijn arbeid</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>gezonde de ziel en de lijf / al komen zij uit een wijf</t>
+          <t>dat zijn al verloren arbeid / ik hebben u nu toe zeggen</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6392,31 +6392,31 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="n">
-        <v>0.6732802547009524</v>
+        <v>0.6727176081476474</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dat overlijt soe cortelike / Verdienen souden hemelrike</t>
+          <t>Ende lant ende stede ende borge te winnen / Daer anders niet inne en leit</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Want nemmermeer en soude / Mensche te hemelrike comen</t>
+          <t>Ende dat si aldaer ter stede / Haer borghen souden bringhen mede</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>dat overlijd zo kortelijk / verdienen zullen hemelrijk</t>
+          <t>en land en stede en borg te winnen / daar anders niet in ne liggen</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>want nimmermeer ne zullen / mens te hemelrijk komen</t>
+          <t>en dat zij aldaar ter stede / haar borg zullen brengen mede</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6432,31 +6432,31 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="n">
-        <v>0.6747290849191689</v>
+        <v>0.673997167923214</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ende gheworpen in die pine / Hoe hem in die helle staet te sine</t>
+          <t>Dat overlijt soe cortelike / Verdienen souden hemelrike</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hem en behoert niet allene te sine / Doen nam hi al sonder pine</t>
+          <t>Want nemmermeer en soude / Mensche te hemelrike comen</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>en werpen in die pijn / hoe hij in die hel staan te zijn</t>
+          <t>dat overlijd zo kortelijk / verdienen zullen hemelrijk</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>hij ne behoren niet alleen te zijn / toen nemen hij al zonder pijn</t>
+          <t>want nimmermeer ne zullen / mens te hemelrijk komen</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6472,31 +6472,31 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
-        <v>0.6758484470299055</v>
+        <v>0.6741547938344656</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>207</v>
+        <v>7</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dat hi mi dan al mine zonden / Verre van mi wille werpen</t>
+          <t>Ende menich boec datmen mint / Daer men luttel orboers in vint</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>En hebbic niet in mi / Al woudic al laten varen</t>
+          <t>Ende meneghe wijsheit daer toe wet / Vindi in dit boec gheset</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>dat hij ik dan al mijn zonde / ver van ik willen werpen</t>
+          <t>en menig boek dat men minnen / daar men luttel oorbaar in vinden</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ne hebben ik niet in ik / al willen ik al laten varen</t>
+          <t>en menig wijsheid daar toe wetten / vinden gij in dit boek zetten</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6512,31 +6512,31 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="n">
-        <v>0.678679715691806</v>
+        <v>0.6742133141629534</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Come te ghenadighen vagheviere / Daerbeit zal mi wesen zwaer</t>
+          <t>Dat hi mi wille verlenen / Macht sin ende ghesonde</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ende saechte ende ghenadech wesen / Ofte sijn rike sal staen in vresen</t>
+          <t>Ghesonde der sielen ende den live / Al comen si uut enen wive</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>komen te genadig vagevuur / daarbeid zullen ik wezen zwaar</t>
+          <t>dat hij ik willen verlenen / macht zin en gezonde</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>en zacht en genadig wezen / ofte zijn rijk zullen staan in vrees</t>
+          <t>gezonde de ziel en de lijf / al komen zij uit een wijf</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6552,31 +6552,31 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="n">
-        <v>0.6804112013191737</v>
+        <v>0.6747408174714731</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ende minen zin also verclaerde / Dat ic dit werc met minen arbeide</t>
+          <t>Dus heeft sy algader / Die drievuldicheit in hare</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Dats al verloren arbeyt / Ic hebt u nu toe gheseyt</t>
+          <t>Dat es volmaect algader / Dit seyt Ihesus Sydrac</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>en mijn zin alzo verklaren / dat ik dit werk met mijn arbeid</t>
+          <t>dus hebben zij algader / die drievuldigheid in haar</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>dat zijn al verloren arbeid / ik hebben u nu toe zeggen</t>
+          <t>dat zijn volmaakt algader / dit zeggen NOU-P NOU-P</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6592,31 +6592,31 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="n">
-        <v>0.6806678867372478</v>
+        <v>0.6761358575830014</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ende netelen ende distelen plucken gaen / Ende die goede vrucht laten staen</t>
+          <t>Nochtan half logene es ende mere / Ende anders en hebben engene lere</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ende met sinen wive gaen / Ende beyde in enen vleesche staen</t>
+          <t>Ghemaect tote onse lere / Seneca seghet die here</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>en netelen en distel plukken gaan / en die goed vrucht laten staan</t>
+          <t>nochtan half leugen zijn en meer / en anders ne hebben negeen leer</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>en met zijn wijf gaan / en beide in een vlees staan</t>
+          <t>maken tot ons leer / NOU-P zeggen die heer</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6632,31 +6632,31 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="n">
-        <v>0.682095711399242</v>
+        <v>0.6761643207887006</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Doe zoene met haren borsten zogede / Daer hi sinen omoet in togede</t>
+          <t>Dat dese edele leringe soude / Den Dietscen lieden verholen wesen</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Daer bi willic uwen oetmoet / Aenscouwen oetmoet es so goet</t>
+          <t>Maer dat sal met bescede wesen / Na dat noet es van desen</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>toen zoenen met haar borst zogen / daar hij zijn ootmoed in togen</t>
+          <t>dat deze edel lering zullen / de Diets lieden verhelen wezen</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>daar bij willen ik uw ootmoed / aanschouwen ootmoed zijn zo goed</t>
+          <t>maar dat zullen met bescheid wezen / na dat NOU-P zijn van deze</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6672,31 +6672,31 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="n">
-        <v>0.6826511643703331</v>
+        <v>0.6764630339396018</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nochtan half logene es ende mere / Ende anders en hebben engene lere</t>
+          <t>Die de dinc te rechte besiet / Die den tijt onledich maken</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ghemaect tote onse lere / Seneca seghet die here</t>
+          <t>Onder die droeve diet wel besiet / Sente Pauwels scrijft daer</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>nochtan half leugen zijn en meer / en anders ne hebben negeen leer</t>
+          <t>die de ding te rechte bezien / die de tijd onledig maken</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>maken tot ons leer / NOU-P zeggen die heer</t>
+          <t>onder die droef die het wel bezien / NOU-P NOU-P schrijven daar</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6712,31 +6712,31 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="n">
-        <v>0.6859796765026998</v>
+        <v>0.6771027290830787</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Die geen Walsch en connen lesen / Noch geen Walsch en verstaen</t>
+          <t>Daer de warelt zal nemen fijn / Ende de welke behouden zal sijn</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dat si daer na dat verstaet / Nemmermeer en doen gheen quaet</t>
+          <t>Hine mochte nemmermeer sijn / Van sijn consten meester fijn</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>die geen Waals ne kunnen lezen / noch geen Waals ne verstaan</t>
+          <t>daar de wereld zullen nemen fijn / en de welk behouden zullen zijn</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>dat zij daar na dat verstaan / nimmermeer ne doen geen kwaad</t>
+          <t>hij ne mogen nimmermeer zijn / van zijn kunst meester fijn</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6752,31 +6752,31 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="n">
-        <v>0.6863858747686052</v>
+        <v>0.6778564340835693</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Die de dinc te rechte besiet / Die den tijt onledich maken</t>
+          <t>Uten Walsce in Dietsce leide / Want ict niewer omme dede</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Onder die droeve diet wel besiet / Sente Pauwels scrijft daer</t>
+          <t>Want mids onvoersienecheyt / Valt die mensche in menech leyt</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>die de ding te rechte bezien / die de tijd onledig maken</t>
+          <t>uit dat wals in Diets leed / want ik het niewer om doen</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>onder die droef die het wel bezien / NOU-P NOU-P schrijven daar</t>
+          <t>want mits onvoorzienigheid / vallen die mens in menig leed</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6792,31 +6792,31 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
-        <v>0.6864900272305543</v>
+        <v>0.6791684413848715</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dus heeft sy algader / Die drievuldicheit in hare</t>
+          <t>Al der goonre dieze lezen / Ic hope God mijn loon sal wezen</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dat es volmaect algader / Dit seyt Ihesus Sydrac</t>
+          <t>Alse hi biden sot es / Also ons Salomon doet gewes</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>dus hebben zij algader / die drievuldigheid in haar</t>
+          <t>al de gonder die zij lezen / ik hopen NOU-P mijn loon zullen wijzen</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>dat zijn volmaakt algader / dit zeggen NOU-P NOU-P</t>
+          <t>als hij bij de zot zijn / alzo ons NOU-P doen wijzen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6832,31 +6832,31 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
-        <v>0.6868643627259305</v>
+        <v>0.6815065338988717</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ende oec die werden verscroven / Ende gheworpen in die pine</t>
+          <t>Dat hi mi dan al mine zonden / Verre van mi wille werpen</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ende die oec werpen onder voet / Ende wijf ende kinder met</t>
+          <t>En hebbic niet in mi / Al woudic al laten varen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>en ook die worden verschruiven / en werpen in die pijn</t>
+          <t>dat hij ik dan al mijn zonde / ver van ik willen werpen</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>en die ook werpen onder voet / en wijf en kind met</t>
+          <t>ne hebben ik niet in ik / al willen ik al laten varen</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6872,31 +6872,31 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
-        <v>0.6869106704035071</v>
+        <v>0.6835726638625814</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dat dese edele leringe soude / Den Dietscen lieden verholen wesen</t>
+          <t>Die geen Walsch en connen lesen / Noch geen Walsch en verstaen</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Maer dat sal met bescede wesen / Na dat noet es van desen</t>
+          <t>Dat si daer na dat verstaet / Nemmermeer en doen gheen quaet</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>dat deze edel lering zullen / de Diets lieden verhelen wezen</t>
+          <t>die geen Waals ne kunnen lezen / noch geen Waals ne verstaan</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>maar dat zullen met bescheid wezen / na dat NOU-P zijn van deze</t>
+          <t>dat zij daar na dat verstaan / nimmermeer ne doen geen kwaad</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6912,31 +6912,31 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
-        <v>0.687151227376388</v>
+        <v>0.6837095206859347</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Al der goonre dieze lezen / Ic hope God mijn loon sal wezen</t>
+          <t>Come te ghenadighen vagheviere / Daerbeit zal mi wesen zwaer</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dander rijcheyt die ic las / Die wilen in Troyen was</t>
+          <t>Ende saechte ende ghenadech wesen / Ofte sijn rike sal staen in vresen</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>al de gonder die zij lezen / ik hopen NOU-P mijn loon zullen wijzen</t>
+          <t>komen te genadig vagevuur / daarbeid zullen ik wezen zwaar</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>de ander rijkheid die ik lezen / die wijlen in NOU-P zijn</t>
+          <t>en zacht en genadig wezen / ofte zijn rijk zullen staan in vrees</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6952,31 +6952,31 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
-        <v>0.6890042250672996</v>
+        <v>0.6851532744608001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sonder rime in slechte woert / Doen werdic daer toe becoert</t>
+          <t>Doe zoene met haren borsten zogede / Daer hi sinen omoet in togede</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dat woert en versta ic niet alsoe / Maer ic segghe aldus daer toe</t>
+          <t>Daer bi willic uwen oetmoet / Aenscouwen oetmoet es so goet</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>zonder rijm in slecht woord / toen worden ik daar toe bekoren</t>
+          <t>toen zoenen met haar borst zogen / daar hij zijn ootmoed in togen</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>dat woord ne verstaan ik niet alzo / maar ik zeggen aldus daar toe</t>
+          <t>daar bij willen ik uw ootmoed / aanschouwen ootmoed zijn zo goed</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6992,31 +6992,31 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
-        <v>0.6894252052405007</v>
+        <v>0.6853044067398624</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Uten Walsce in Dietsce leide / Want ict niewer omme dede</t>
+          <t>Hoe der inglen coor sijn gheheten / Dit was hem algader cont</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Want mids onvoersienecheyt / Valt die mensche in menech leyt</t>
+          <t>Ghemaect uwen vianden cont / Dien mochti oec muteren</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>uit dat wals in Diets leed / want ik het niewer om doen</t>
+          <t>hoe de engel koor zijn heten / dit zijn hij algader kond</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>want mits onvoorzienigheid / vallen die mens in menig leed</t>
+          <t>maken uw vijand kond / dat mogen gij ook muteren</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7032,7 +7032,7 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
-        <v>0.6901404296227398</v>
+        <v>0.6853484403489905</v>
       </c>
     </row>
     <row r="166">
@@ -7072,31 +7072,31 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
-        <v>0.6915912017414971</v>
+        <v>0.6860645556299726</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Daer de warelt zal nemen fijn / Ende de welke behouden zal sijn</t>
+          <t>Sonder rime in slechte woert / Doen werdic daer toe becoert</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hine mochte nemmermeer sijn / Van sijn consten meester fijn</t>
+          <t>Dat woert en versta ic niet alsoe / Maer ic segghe aldus daer toe</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>daar de wereld zullen nemen fijn / en de welk behouden zullen zijn</t>
+          <t>zonder rijm in slecht woord / toen worden ik daar toe bekoren</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>hij ne mogen nimmermeer zijn / van zijn kunst meester fijn</t>
+          <t>dat woord ne verstaan ik niet alzo / maar ik zeggen aldus daar toe</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7112,7 +7112,7 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="n">
-        <v>0.6916555226812046</v>
+        <v>0.6890875931129825</v>
       </c>
     </row>
     <row r="168">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dat ic u met mire pine / In dietsche vertrecke so ic best can</t>
+          <t>Dats al verloren arbeyt / Ic hebt u nu toe gheseyt</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>dat ik u met mijn pijn / in Diets vertrekken zo ik goed kunnen</t>
+          <t>dat zijn al verloren arbeid / ik hebben u nu toe zeggen</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7152,31 +7152,31 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
-        <v>0.6920682639711461</v>
+        <v>0.6895846961778288</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Daer men ginder af ontfaet / Hondertfout van lone</t>
+          <t>Doen ic dit werc ierst began / Ende hebbe versleten nochtan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Die wel doet hi sal ontfaen / Loen daer af dats sonder waen</t>
+          <t>Laet ons yrst aent hoeft beghinnen / Der meester raet van Surgyen</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>daar men ginder af ontvangen / honderdfout van loon</t>
+          <t>toen ik dit werk eerst beginnen / en hebben verslijten nochtan</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>die wel doen hij zullen ontvangen / loenen daar af dat zijn zonder waan</t>
+          <t>laten ons eerst aan het hoofd beginnen / de meester raad van NOU-P</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7192,31 +7192,31 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="n">
-        <v>0.6956558964354458</v>
+        <v>0.6910601056786947</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Hoe der inglen coor sijn gheheten / Dit was hem algader cont</t>
+          <t>Ende ierstwerven int scrift leide / Die de materie sal leggen wale</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ghemaect uwen vianden cont / Dien mochti oec muteren</t>
+          <t>Ende so soudic in bedroeftheyden / Seker al minen tijt so leyden</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>hoe de engel koor zijn heten / dit zijn hij algader kond</t>
+          <t>en eerstwerf in het schrift leiden / die de materie zullen leggen wel</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>maken uw vijand kond / dat mogen gij ook muteren</t>
+          <t>en zo zullen ik in bedroefdheid / zeker al mijn tijd zo leiden</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7232,31 +7232,31 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
-        <v>0.6966148104873411</v>
+        <v>0.6913975199234569</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Daer omme behoren sy ten vroeden / Die ghene die hem hier soe spoeden</t>
+          <t>Die met vruchten sijn bewaert / Ende netelen ende distelen plucken gaen</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Soe eest u scande sidi vroet / Daer om en es niet so goet</t>
+          <t>Die vele wijsheden segghen can / Dat die ghene wel es bewaert</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>daar om behoren zij ten vroed / die gene die hij hier zo spoeden</t>
+          <t>die met vrucht zijn bewaren / en netelen en distel plukken gaan</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>zo zijn het u schande zijn gij vroed / daar om ne zijn niet zo goed</t>
+          <t>die veel wijsheid zeggen kunnen / dat die gene wel zijn bewaren</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7272,31 +7272,31 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
-        <v>0.6970940201090974</v>
+        <v>0.6918282128758897</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ende vele meer dan ontsint / Die dese vrouwe niet en mint</t>
+          <t>Daer men ginder af ontfaet / Hondertfout van lone</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Daer en es niet dan kijnscheyt in / Ende si minnen spade ende vroe</t>
+          <t>Die wel doet hi sal ontfaen / Loen daer af dats sonder waen</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>en veel meer dan ontzinnen / die deze vrouwe niet ne minnen</t>
+          <t>daar men ginder af ontvangen / honderdfout van loon</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>daar ne zijn niet dan kinsheid en / en zij minnen spa en vroe</t>
+          <t>die wel doen hij zullen ontvangen / loenen daar af dat zijn zonder waan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7312,31 +7312,31 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>0.6978296798342389</v>
+        <v>0.6934832362328591</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Doen ic dit werc ierst began / Ende hebbe versleten nochtan</t>
+          <t>Daer omme behoren sy ten vroeden / Die ghene die hem hier soe spoeden</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Laet ons yrst aent hoeft beghinnen / Der meester raet van Surgyen</t>
+          <t>Soe eest u scande sidi vroet / Daer om en es niet so goet</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>toen ik dit werk eerst beginnen / en hebben verslijten nochtan</t>
+          <t>daar om behoren zij ten vroed / die gene die hij hier zo spoeden</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>laten ons eerst aan het hoofd beginnen / de meester raad van NOU-P</t>
+          <t>zo zijn het u schande zijn gij vroed / daar om ne zijn niet zo goed</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7352,31 +7352,31 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
-        <v>0.698031349787577</v>
+        <v>0.694293148779499</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>In weet wat sire inne menen / Dese slachten wel den genen</t>
+          <t>Ende oec die werden verscroven / Ende gheworpen in die pine</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>So eest wel te wetene dan / Dat sinen viant gheen man</t>
+          <t>Ende die oec werpen onder voet / Ende wijf ende kinder met</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>u weten wat zijn ik ne menen / deze slachten wel de geen</t>
+          <t>en ook die worden verschruiven / en werpen in die pijn</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>zo zijn het wel te weten dan / dat zijn vijand geen man</t>
+          <t>en die ook werpen onder voet / en wijf en kind met</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7392,31 +7392,31 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
-        <v>0.6992965070032495</v>
+        <v>0.694346830470173</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wast dat ic dit translateerde / Doe men Gods iare noteerde</t>
+          <t>Ende hoe si ter bliscap sullen comen / Metten inglen daer boven</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Dat hi dit boec maecte int jaer / Xijc dat ghi dat wet</t>
+          <t>Dien God onse Here seynt van boven / Ic seyde u oec datmen soude</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>wassen dat ik dit translateren / toen men NOU-P jaar noteren</t>
+          <t>en hoe zij ter blijdschap zullen komen / met de engel daar boven</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>dat hij dit boek maken in het jaar / tweeëntwintig dat gij dat wetten</t>
+          <t>dat NOU-P ons NOU-P zenden van boven / ik zeggen u ook dat men zullen</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7432,31 +7432,31 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
-        <v>0.6998845424863203</v>
+        <v>0.6965918749465282</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Die met vruchten sijn bewaert / Ende netelen ende distelen plucken gaen</t>
+          <t>Wast dat ic dit translateerde / Doe men Gods iare noteerde</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Die vele wijsheden segghen can / Dat die ghene wel es bewaert</t>
+          <t>Dat hi dit boec maecte int jaer / Xijc dat ghi dat wet</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>die met vrucht zijn bewaren / en netelen en distel plukken gaan</t>
+          <t>wassen dat ik dit translateren / toen men NOU-P jaar noteren</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>die veel wijsheid zeggen kunnen / dat die gene wel zijn bewaren</t>
+          <t>dat hij dit boek maken in het jaar / tweeëntwintig dat gij dat wetten</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7472,31 +7472,31 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
-        <v>0.7009087513802121</v>
+        <v>0.6985582845359213</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ende hoe sy inden soude met allen / Van firmamenten ende van planeten</t>
+          <t>Dit was hem algader cont / Hout voor eenen vont</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ende alle quaetheyt bringhen inne / Seneca spreect van desen</t>
+          <t>Den wech die u niet en es cont / Oec so seghet een wijs here</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>en hoe zij innen zullen met al / van firmament en van planeet</t>
+          <t>dit zijn hij algader kond / hout voor een vont</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>en al kwaadheid brengen innen / NOU-P spreken van deze</t>
+          <t>de weg die u niet ne zijn kond / ook zo zeggen een wijs heer</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7512,31 +7512,31 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
-        <v>0.7016118294154297</v>
+        <v>0.7003553501156364</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ende ierstwerven int scrift leide / Die de materie sal leggen wale</t>
+          <t>Selen ginder luttel mayen / Daer omme behoren sy ten vroeden</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ende so soudic in bedroeftheyden / Seker al minen tijt so leyden</t>
+          <t>Want vele liede sijn meer vroet / Dan luttel wildijt verstaen</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>en eerstwerf in het schrift leiden / die de materie zullen leggen wel</t>
+          <t>zullen ginder luttel maaien / daar om behoren zij ten vroed</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>en zo zullen ik in bedroefdheid / zeker al mijn tijd zo leiden</t>
+          <t>want veel lieden zijn meer vroed / dan luttel willen verstaan</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7552,31 +7552,31 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="n">
-        <v>0.7017071143039481</v>
+        <v>0.7013834919136146</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Daer boven inden oversten trone / Daer die ingelen singen hoge</t>
+          <t>Te sayene dat goede sait / Daer men ginder af ontfaet</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>In die overste godheyde / Daer hi seker waer aen seyde</t>
+          <t>Die wel doet hi sal ontfaen / Loen daer af dats sonder waen</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>daar boven in de overst troon / daar die engel zingen hoog</t>
+          <t>te NOU-P dat goed zaad / daar men ginder af ontvangen</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>in die overst godheid / daar hij zeker waar aan zeggen</t>
+          <t>die wel doen hij zullen ontvangen / loenen daar af dat zijn zonder waan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7592,31 +7592,31 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
-        <v>0.7017104528938553</v>
+        <v>0.7015265098162606</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>43</v>
+        <v>173</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Te sayene dat goede sait / Daer men ginder af ontfaet</t>
+          <t>Ende vele meer dan ontsint / Die dese vrouwe niet en mint</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Die wel doet hi sal ontfaen / Loen daer af dats sonder waen</t>
+          <t>Daer en es niet dan kijnscheyt in / Ende si minnen spade ende vroe</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>te NOU-P dat goed zaad / daar men ginder af ontvangen</t>
+          <t>en veel meer dan ontzinnen / die deze vrouwe niet ne minnen</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>die wel doen hij zullen ontvangen / loenen daar af dat zijn zonder waan</t>
+          <t>daar ne zijn niet dan kinsheid en / en zij minnen spa en vroe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7632,31 +7632,31 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
-        <v>0.7034296961502078</v>
+        <v>0.7016211124946101</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Selen ginder luttel mayen / Daer omme behoren sy ten vroeden</t>
+          <t>In weet wat sire inne menen / Dese slachten wel den genen</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Want vele liede sijn meer vroet / Dan luttel wildijt verstaen</t>
+          <t>So eest wel te wetene dan / Dat sinen viant gheen man</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>zullen ginder luttel maaien / daar om behoren zij ten vroed</t>
+          <t>u weten wat zijn ik ne menen / deze slachten wel de geen</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>want veel lieden zijn meer vroed / dan luttel willen verstaan</t>
+          <t>zo zijn het wel te weten dan / dat zijn vijand geen man</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7672,31 +7672,31 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
-        <v>0.7036761954488869</v>
+        <v>0.7020179992846286</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Die de materie sal leggen wale / Van ere tale in een ander tale</t>
+          <t>Ende hoe sy inden soude met allen / Van firmamenten ende van planeten</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Met uwer talen si es so lanc / Ghi singhet al enen sanc</t>
+          <t>Ende alle quaetheyt bringhen inne / Seneca spreect van desen</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>die de materie zullen leggen wel / van een taal in een ander taal</t>
+          <t>en hoe zij innen zullen met al / van firmament en van planeet</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>met u taal zij zijn zo lang / gij zingen al een zang</t>
+          <t>en al kwaadheid brengen innen / NOU-P spreken van deze</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7712,31 +7712,31 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="n">
-        <v>0.7038057518642085</v>
+        <v>0.7023662169031226</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>In sine glorie ewelike / Dat hi mi so langhe spaerde</t>
+          <t>Want ic oud was vichtich iaer / Doen ic dit werc ierst began</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Dat ghijs ewelic sult hebben ere / Melibeus antworde die here</t>
+          <t>Laet ons yrst aent hoeft beghinnen / Der meester raet van Surgyen</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>in zijn glorie eeuwelijk / dat hij ik zo lang sparen</t>
+          <t>want ik oud zijn vijftig jaar / toen ik dit werk eerst beginnen</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>dat gij dat eeuwelijk zullen hebben een / NOU-P antwoorden die heer</t>
+          <t>laten ons eerst aan het hoofd beginnen / de meester raad van NOU-P</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7752,31 +7752,31 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
-        <v>0.7045851905298639</v>
+        <v>0.7038110392280399</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dit was hem algader cont / Hout voor eenen vont</t>
+          <t>In sine glorie ewelike / Dat hi mi so langhe spaerde</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Den wech die u niet en es cont / Oec so seghet een wijs here</t>
+          <t>Dat ghijs ewelic sult hebben ere / Melibeus antworde die here</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>dit zijn hij algader kond / hout voor een vont</t>
+          <t>in zijn glorie eeuwelijk / dat hij ik zo lang sparen</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>de weg die u niet ne zijn kond / ook zo zeggen een wijs heer</t>
+          <t>dat gij dat eeuwelijk zullen hebben een / NOU-P antwoorden die heer</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7792,31 +7792,31 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
-        <v>0.7063375165878489</v>
+        <v>0.7048418222237656</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ende hoe si ter bliscap sullen comen / Metten inglen daer boven</t>
+          <t>Die de materie sal leggen wale / Van ere tale in een ander tale</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Dien God onse Here seynt van boven / Ic seyde u oec datmen soude</t>
+          <t>Met uwer talen si es so lanc / Ghi singhet al enen sanc</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>en hoe zij ter blijdschap zullen komen / met de engel daar boven</t>
+          <t>die de materie zullen leggen wel / van een taal in een ander taal</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>dat NOU-P ons NOU-P zenden van boven / ik zeggen u ook dat men zullen</t>
+          <t>met u taal zij zijn zo lang / gij zingen al een zang</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7832,31 +7832,31 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
-        <v>0.7074510100562719</v>
+        <v>0.705846305731648</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Want ic oud was vichtich iaer / Doen ic dit werc ierst began</t>
+          <t>Daer boven inden oversten trone / Daer die ingelen singen hoge</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Laet ons yrst aent hoeft beghinnen / Der meester raet van Surgyen</t>
+          <t>In die overste godheyde / Daer hi seker waer aen seyde</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>want ik oud zijn vijftig jaar / toen ik dit werk eerst beginnen</t>
+          <t>daar boven in de overst troon / daar die engel zingen hoog</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>laten ons eerst aan het hoofd beginnen / de meester raad van NOU-P</t>
+          <t>in die overst godheid / daar hij zeker waar aan zeggen</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7872,31 +7872,31 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
-        <v>0.7113925353114958</v>
+        <v>0.7084425570681805</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Die de bybele ende menich ander werc / Int latijn dichte als een clerc</t>
+          <t>Ic hope God mijn loon sal wezen / Ende ic bidde hem allen met trauwen</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Die Ioden wildijt weten / Hebben Bibelen ende Propheten</t>
+          <t>Alse hi biden sot es / Also ons Salomon doet gewes</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>die de bijbel en menig ander werk / in het latijn dichten als een klerk</t>
+          <t>ik hopen NOU-P mijn loon zullen wijzen / en ik bidden hij al met trouw</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>die jood willen weten / hebben Bijbel en profeet</t>
+          <t>als hij bij de zot zijn / alzo ons NOU-P doen wijzen</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7912,31 +7912,31 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
-        <v>0.7118484783670935</v>
+        <v>0.7097778505929435</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>O Maria reine vat / Wanen soe quam u dat</t>
+          <t>Die de bybele ende menich ander werc / Int latijn dichte als een clerc</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Al dunct u in uwen waen / Dat u davonture wel heeft ghedaen</t>
+          <t>Mesdoedi dat sal hi merken / Eest in worden of in werken</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>o NOU-P rein vat / waan zo komen u dat</t>
+          <t>die de bijbel en menig ander werk / in het latijn dichten als een klerk</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>al dunken u in uw waan / dat u de avontuur wel hebben doen</t>
+          <t>misdoedi dat zullen hij merken / zijn het in woord of in werk</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7952,31 +7952,31 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
-        <v>0.7123784130782789</v>
+        <v>0.7117096032286869</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dat hi mi so langhe spaerde / Ende minen zin also verclaerde</t>
+          <t>O Maria reine vat / Wanen soe quam u dat</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>HEre hier vore seydic u dat / Nu willict u verclaren bat</t>
+          <t>Al dunct u in uwen waen / Dat u davonture wel heeft ghedaen</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>dat hij ik zo lang sparen / en mijn zin alzo verklaren</t>
+          <t>o NOU-P rein vat / waan zo komen u dat</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>heer hier voor zeggen ik u dat / nu willen ik u verklaren bet</t>
+          <t>al dunken u in uw waan / dat u de avontuur wel hebben doen</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7992,31 +7992,31 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
-        <v>0.7123956233933271</v>
+        <v>0.7124032022973785</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Dat sy selen daer omme bedi / Vriendelike bidden voir my</t>
+          <t>Dat hi mi so langhe spaerde / Ende minen zin also verclaerde</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dat ic den rechtere bidden soude / Dat hi mi hier af wreken woude</t>
+          <t>Ende ghebieden hem dat si varen / Over die zee sonder enech sparen</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>dat zij zullen daar om bedie / vriendelijk bidden voor ik</t>
+          <t>dat hij ik zo lang sparen / en mijn zin alzo verklaren</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>dat ik de rechter bidden zullen / dat hij ik hier af wreken willen</t>
+          <t>en gebieden hij dat zij varen / over die zee zonder enig sparen</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8032,31 +8032,31 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="n">
-        <v>0.7147582210430733</v>
+        <v>0.7126337166478212</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ic hope God mijn loon sal wezen / Ende ic bidde hem allen met trauwen</t>
+          <t>Dat sy selen daer omme bedi / Vriendelike bidden voir my</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Alse hi biden sot es / Also ons Salomon doet gewes</t>
+          <t>Dat ic den rechtere bidden soude / Dat hi mi hier af wreken woude</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ik hopen NOU-P mijn loon zullen wijzen / en ik bidden hij al met trouw</t>
+          <t>dat zij zullen daar om bedie / vriendelijk bidden voor ik</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>als hij bij de zot zijn / alzo ons NOU-P doen wijzen</t>
+          <t>dat ik de rechter bidden zullen / dat hij ik hier af wreken willen</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8072,31 +8072,31 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="n">
-        <v>0.7186697919672013</v>
+        <v>0.7154951877598867</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Van ere tale in een ander tale / Die sal den text leggen dan</t>
+          <t>Verdienen souden hemelrike / Ende die hier luttel sayen</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Met uwer talen si es so lanc / Ghi singhet al enen sanc</t>
+          <t>Want nemmermeer en soude / Mensche te hemelrike comen</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>van een taal in een ander taal / die zullen de tekst leggen dan</t>
+          <t>verdienen zullen hemelrijk / en die hier luttel zaaien</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>met u taal zij zijn zo lang / gij zingen al een zang</t>
+          <t>want nimmermeer ne zullen / mens te hemelrijk komen</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8112,31 +8112,31 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="n">
-        <v>0.720176425531053</v>
+        <v>0.7213865313412585</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Metten inglen daer boven / Ende oec die werden verscroven</t>
+          <t>Van ere tale in een ander tale / Die sal den text leggen dan</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bescrijft oec Seneca / Die boven al dat leeft</t>
+          <t>Met uwer talen si es so lanc / Ghi singhet al enen sanc</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>met de engel daar boven / en ook die worden verschruiven</t>
+          <t>van een taal in een ander taal / die zullen de tekst leggen dan</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>beschrijven ook NOU-P / die boven al dat leven</t>
+          <t>met u taal zij zijn zo lang / gij zingen al een zang</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8152,31 +8152,31 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
-        <v>0.7206841390826102</v>
+        <v>0.7218057310652427</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Verdienen souden hemelrike / Ende die hier luttel sayen</t>
+          <t>Metten inglen daer boven / Ende oec die werden verscroven</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Want nemmermeer en soude / Mensche te hemelrike comen</t>
+          <t>Bescrijft oec Seneca / Die boven al dat leeft</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>verdienen zullen hemelrijk / en die hier luttel zaaien</t>
+          <t>met de engel daar boven / en ook die worden verschruiven</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>want nimmermeer ne zullen / mens te hemelrijk komen</t>
+          <t>beschrijven ook NOU-P / die boven al dat leven</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8192,7 +8192,7 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="n">
-        <v>0.7223523321262715</v>
+        <v>0.723544311500161</v>
       </c>
     </row>
     <row r="195">
@@ -8232,7 +8232,7 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="n">
-        <v>0.7362533561191168</v>
+        <v>0.7294920204024946</v>
       </c>
     </row>
     <row r="196">
@@ -8272,7 +8272,7 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="n">
-        <v>0.736424652048402</v>
+        <v>0.7343358013604691</v>
       </c>
     </row>
     <row r="197">
@@ -8312,31 +8312,31 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="n">
-        <v>0.7402188788608117</v>
+        <v>0.7378987634246856</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ende die hier luttel sayen / Selen ginder luttel mayen</t>
+          <t>Daerbeit zal mi wesen zwaer / Want ic oud was vichtich iaer</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Dan luttel wildijt verstaen / Oec salmen dicke te rade gaen</t>
+          <t>Hemelrijc dat es waer / Haer en es niet te swaer</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>en die hier luttel zaaien / zullen ginder luttel maaien</t>
+          <t>daarbeid zullen ik wezen zwaar / want ik oud zijn vijftig jaar</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>dan luttel willen verstaan / ook zullen men dik te raad gaan</t>
+          <t>hemelrijk dat zijn waar / zij ne zijn niet te zwaar</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8352,31 +8352,31 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="n">
-        <v>0.7454663843794166</v>
+        <v>0.7387769950545584</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Daerbeit zal mi wesen zwaer / Want ic oud was vichtich iaer</t>
+          <t>Anders danse die makere seide / Ende ierstwerven int scrift leide</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hemelrijc dat es waer / Haer en es niet te swaer</t>
+          <t>Ende so soudic in bedroeftheyden / Seker al minen tijt so leyden</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>daarbeid zullen ik wezen zwaar / want ik oud zijn vijftig jaar</t>
+          <t>anders dans die maker zeggen / en eerstwerf in het schrift leiden</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>hemelrijk dat zijn waar / zij ne zijn niet te zwaar</t>
+          <t>en zo zullen ik in bedroefdheid / zeker al mijn tijd zo leiden</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8392,7 +8392,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="n">
-        <v>0.7456877607410282</v>
+        <v>0.7454475836715101</v>
       </c>
     </row>
     <row r="200">
@@ -8432,31 +8432,31 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="n">
-        <v>0.7474044717144078</v>
+        <v>0.7462131273520052</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Die ghene die hem hier soe spoeden / Te sayene dat goede sait</t>
+          <t>Dat ic daer naer sciere / Come te ghenadighen vagheviere</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>So staet die dinc twifelike / Hebdijt oec jeghen die ghene</t>
+          <t>Mijn here sal u sijn ghenadich / Daer en twifelt u niet an</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>die gene die hij hier zo spoeden / te NOU-P dat goed zaad</t>
+          <t>dat ik daar naar schieren / komen te genadig vagevuur</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>zo staan die ding twijfellijk / hebben gij ook jegen die gene</t>
+          <t>mijn heer zullen u zijn genadig / daar ne twijfelen u niet aan</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8472,31 +8472,31 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="n">
-        <v>0.747696457314861</v>
+        <v>0.7478973717809723</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Dat ic daer naer sciere / Come te ghenadighen vagheviere</t>
+          <t>Sonder rime alsoe ic sach / Dat hy inden Walsce lach</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Mijn here sal u sijn ghenadich / Daer en twifelt u niet an</t>
+          <t>Want hi spreect als men daer siet / Sonder mi en moghedi doen niet</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>dat ik daar naar schieren / komen te genadig vagevuur</t>
+          <t>zonder rijm alzo ik zien / dat hij in de wals lachen</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>mijn heer zullen u zijn genadig / daar ne twijfelen u niet aan</t>
+          <t>want hij spreken als men daar zien / zonder ik ne mogen gij doen niet</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8512,31 +8512,31 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="n">
-        <v>0.7477179146240006</v>
+        <v>0.7480462047572896</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ende mijn leven betren zoe / Dat ic daer naer sciere</t>
+          <t>Die ghene die hem hier soe spoeden / Te sayene dat goede sait</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Prudentia sprac daer naer / Die warenesse daer men met</t>
+          <t>So staet die dinc twifelike / Hebdijt oec jeghen die ghene</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>en mijn leven beteren zo / dat ik daar naar schieren</t>
+          <t>die gene die hij hier zo spoeden / te NOU-P dat goed zaad</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>NOU-P spreken daar naar / die waarnis daar men met</t>
+          <t>zo staan die ding twijfellijk / hebben gij ook jegen die gene</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8552,31 +8552,31 @@
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="n">
-        <v>0.7501054624180008</v>
+        <v>0.7485449821479035</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Sonder rime alsoe ic sach / Dat hy inden Walsce lach</t>
+          <t>Ende die hier luttel sayen / Selen ginder luttel mayen</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Want hi spreect als men daer siet / Sonder mi en moghedi doen niet</t>
+          <t>Dan luttel wildijt verstaen / Oec salmen dicke te rade gaen</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>zonder rijm alzo ik zien / dat hij in de wals lachen</t>
+          <t>en die hier luttel zaaien / zullen ginder luttel maaien</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>want hij spreken als men daar zien / zonder ik ne mogen gij doen niet</t>
+          <t>dan luttel willen verstaan / ook zullen men dik te raad gaan</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8592,31 +8592,31 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="n">
-        <v>0.7521663885529107</v>
+        <v>0.7510953945481906</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Anders danse die makere seide / Ende ierstwerven int scrift leide</t>
+          <t>Ende mijn leven betren zoe / Dat ic daer naer sciere</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ende so soudic in bedroeftheyden / Seker al minen tijt so leyden</t>
+          <t>Prudentia sprac daer naer / Die warenesse daer men met</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>anders dans die maker zeggen / en eerstwerf in het schrift leiden</t>
+          <t>en mijn leven beteren zo / dat ik daar naar schieren</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>en zo zullen ik in bedroefdheid / zeker al mijn tijd zo leiden</t>
+          <t>NOU-P spreken daar naar / die waarnis daar men met</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8632,7 +8632,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="n">
-        <v>0.7565721007393935</v>
+        <v>0.7518029378594389</v>
       </c>
     </row>
     <row r="206">
@@ -8672,7 +8672,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="n">
-        <v>0.7587596313556472</v>
+        <v>0.764003303733009</v>
       </c>
     </row>
     <row r="207">
@@ -8712,7 +8712,7 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="n">
-        <v>0.7628073168070634</v>
+        <v>0.7653778675648146</v>
       </c>
     </row>
     <row r="208">
@@ -8752,7 +8752,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="n">
-        <v>0.7892683607561921</v>
+        <v>0.7940588793904698</v>
       </c>
     </row>
     <row r="209">
@@ -8792,7 +8792,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="n">
-        <v>0.8096663212257114</v>
+        <v>0.8072262836196848</v>
       </c>
     </row>
     <row r="210">
@@ -8832,31 +8832,31 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="n">
-        <v>0.826491038232142</v>
+        <v>0.8274735967803195</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Die vriendelijc up hare louch / Doe zoene met haren borsten zogede</t>
+          <t>Ende oec eenderhande sotterie / Die men sonder astronomie</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hoe die dinc was ghevallen / Ende bat vriendelike hen allen</t>
+          <t>Also vier en es sonder roec / Die wise Seneca seghet oec</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>die vriendelijk op haar loeg / toen zoenen met haar borst zogen</t>
+          <t>en ook enerhande zotterij / die men zonder astronomie</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>hoe die ding zijn vallen / en batten vriendelijk zij al</t>
+          <t>alzo vier ne zijn zonder roek / die wijze NOU-P zeggen ook</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -8872,31 +8872,31 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="n">
-        <v>0.8463719788280861</v>
+        <v>0.848885391239006</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ende oec eenderhande sotterie / Die men sonder astronomie</t>
+          <t>Die vriendelijc up hare louch / Doe zoene met haren borsten zogede</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Also vier en es sonder roec / Die wise Seneca seghet oec</t>
+          <t>Hoe die dinc was ghevallen / Ende bat vriendelike hen allen</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>en ook enerhande zotterij / die men zonder astronomie</t>
+          <t>die vriendelijk op haar loeg / toen zoenen met haar borst zogen</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>alzo vier ne zijn zonder roek / die wijze NOU-P zeggen ook</t>
+          <t>hoe die ding zijn vallen / en batten vriendelijk zij al</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -8912,7 +8912,7 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="n">
-        <v>0.8470582919848196</v>
+        <v>0.8497964755786511</v>
       </c>
     </row>
     <row r="213">
@@ -8952,7 +8952,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="n">
-        <v>0.8532425650028556</v>
+        <v>0.8533162224227587</v>
       </c>
     </row>
   </sheetData>
